--- a/cashflow_templates/A_月次資金繰り表_25か月.xlsx
+++ b/cashflow_templates/A_月次資金繰り表_25か月.xlsx
@@ -79,17 +79,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -143,27 +143,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="游ゴシック"/>
+        <b val="1"/>
+        <color rgb="00C00000"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -250,64 +259,69 @@
         <t>運転資金の目安（例：月商の1〜2か月分）を入力。</t>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
+    <comment ref="B9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2025年分/10月」【営業回覧用】業績連動賞与_実績10 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2025年分/11月」【営業回覧用】業績連動賞与_実績11 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2025年分/12月」【営業回覧用】業績連動賞与_実績12 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/1月」【営業回覧用】業績連動賞与_実績1 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/2月」【営業回覧用】業績連動賞与_実績2 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/3月」【営業回覧用】業績連動賞与_実績3 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/4月」【営業回覧用】業績連動賞与_実績4 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/5月」【営業回覧用】業績連動賞与_実績5 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="J9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/6月」【営業回覧用】業績連動賞与_実績6 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/7月」【営業回覧用】業績連動賞与_実績7 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="1" shapeId="0">
+      <text>
+        <t>出典：Google Drive「業績連動賞与/2026年分/8月」【営業回覧用】業績連動賞与_実績8 の合計行「入金実績」</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
       <text>
         <t>初月のみ手入力（期首の現預金残高）。2か月目以降は自動。</t>
       </text>
     </comment>
-    <comment ref="B10" authorId="1" shapeId="0">
+    <comment ref="B53" authorId="0" shapeId="0">
       <text>
-        <t>出典：Google Drive「業績連動賞与/2025年分/10月」【営業回覧用】業績連動賞与_実績10 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2025年分/11月」【営業回覧用】業績連動賞与_実績11 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2025年分/12月」【営業回覧用】業績連動賞与_実績12 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/1月」【営業回覧用】業績連動賞与_実績1 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/2月」【営業回覧用】業績連動賞与_実績2 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/3月」【営業回覧用】業績連動賞与_実績3 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="H10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/4月」【営業回覧用】業績連動賞与_実績4 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="I10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/5月」【営業回覧用】業績連動賞与_実績5 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="J10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/6月」【営業回覧用】業績連動賞与_実績6 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="K10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/7月」【営業回覧用】業績連動賞与_実績7 の合計行「入金実績」</t>
-      </text>
-    </comment>
-    <comment ref="L10" authorId="1" shapeId="0">
-      <text>
-        <t>出典：Google Drive「業績連動賞与/2026年分/8月」【営業回覧用】業績連動賞与_実績8 の合計行「入金実績」</t>
+        <t>期首時点で既に滞納がある場合は、その額を初月の「本来の納付額」に上乗せして入力。</t>
       </text>
     </comment>
   </commentList>
@@ -603,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -648,7 +662,7 @@
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. B8（初月の前月繰越）に期首の現預金残高を入力</t>
+          <t xml:space="preserve">  2. 下部の「前月繰越」行の B47（初月）に期首の現預金残高を入力</t>
         </is>
       </c>
     </row>
@@ -662,47 +676,54 @@
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ※営業収入＝業績連動賞与の集計ファイルの「入金実績」合計（2025年10月〜2026年8月は入力済み）</t>
+          <t xml:space="preserve">  5. 保険料・税を払えなかった月は、下部「滞納管理」に本来の納付額と実際の納付額を入力 → 滞納残高・実質残高が自動計算</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ※営業収入＝業績連動賞与の集計ファイルの「入金実績」合計（2025年10月〜2026年8月は入力済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  4. 翌月繰越がマイナス／最低必要残高未満の月は赤表示 → 借入・支払条件の見直し等を検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>■ 未払金支払：経費の後払い分（カード払い・月末締め翌月払いの外注費・リース料など）の支払額を、実際に口座から出る月に入力します。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>■ 未払金支払：経費の後払い分（カード払い・月末締め翌月払いの外注費・リース料など）の支払額を、実際に口座から出る月に入力します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>■ 科目名は自社に合わせて書き換えて構いません（A列）。行を挿入した場合は「計」の範囲を確認してください。</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>入力セル（黄色・青字）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>計算式セル（白・黒字）＝触らない</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>残高が「最低必要残高」を下回ると赤く表示されます</t>
         </is>
@@ -719,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -906,183 +927,111 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>前月繰越（月初残高）</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="14">
-        <f>B48</f>
-        <v/>
-      </c>
-      <c r="D8" s="14">
-        <f>C48</f>
-        <v/>
-      </c>
-      <c r="E8" s="14">
-        <f>D48</f>
-        <v/>
-      </c>
-      <c r="F8" s="14">
-        <f>E48</f>
-        <v/>
-      </c>
-      <c r="G8" s="14">
-        <f>F48</f>
-        <v/>
-      </c>
-      <c r="H8" s="14">
-        <f>G48</f>
-        <v/>
-      </c>
-      <c r="I8" s="14">
-        <f>H48</f>
-        <v/>
-      </c>
-      <c r="J8" s="14">
-        <f>I48</f>
-        <v/>
-      </c>
-      <c r="K8" s="14">
-        <f>J48</f>
-        <v/>
-      </c>
-      <c r="L8" s="14">
-        <f>K48</f>
-        <v/>
-      </c>
-      <c r="M8" s="14">
-        <f>L48</f>
-        <v/>
-      </c>
-      <c r="N8" s="14">
-        <f>M48</f>
-        <v/>
-      </c>
-      <c r="O8" s="14">
-        <f>N48</f>
-        <v/>
-      </c>
-      <c r="P8" s="14">
-        <f>O48</f>
-        <v/>
-      </c>
-      <c r="Q8" s="14">
-        <f>P48</f>
-        <v/>
-      </c>
-      <c r="R8" s="14">
-        <f>Q48</f>
-        <v/>
-      </c>
-      <c r="S8" s="14">
-        <f>R48</f>
-        <v/>
-      </c>
-      <c r="T8" s="14">
-        <f>S48</f>
-        <v/>
-      </c>
-      <c r="U8" s="14">
-        <f>T48</f>
-        <v/>
-      </c>
-      <c r="V8" s="14">
-        <f>U48</f>
-        <v/>
-      </c>
-      <c r="W8" s="14">
-        <f>V48</f>
-        <v/>
-      </c>
-      <c r="X8" s="14">
-        <f>W48</f>
-        <v/>
-      </c>
-      <c r="Y8" s="14">
-        <f>X48</f>
-        <v/>
-      </c>
-      <c r="Z8" s="14">
-        <f>Y48</f>
-        <v/>
-      </c>
-      <c r="AA8" s="14">
-        <f>B8</f>
-        <v/>
-      </c>
+          <t>経常収支</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
+      <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="14" t="n"/>
+      <c r="S8" s="14" t="n"/>
+      <c r="T8" s="14" t="n"/>
+      <c r="U8" s="14" t="n"/>
+      <c r="V8" s="14" t="n"/>
+      <c r="W8" s="14" t="n"/>
+      <c r="X8" s="14" t="n"/>
+      <c r="Y8" s="14" t="n"/>
+      <c r="Z8" s="14" t="n"/>
+      <c r="AA8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>経常収支</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="16" t="n"/>
-      <c r="R9" s="16" t="n"/>
-      <c r="S9" s="16" t="n"/>
-      <c r="T9" s="16" t="n"/>
-      <c r="U9" s="16" t="n"/>
-      <c r="V9" s="16" t="n"/>
-      <c r="W9" s="16" t="n"/>
-      <c r="X9" s="16" t="n"/>
-      <c r="Y9" s="16" t="n"/>
-      <c r="Z9" s="16" t="n"/>
-      <c r="AA9" s="16" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入｜営業収入</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>11571200</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>12729500</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>10817650</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>7592596</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>12008250</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>14734304</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>14492300</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>9738050</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>12227100</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>7979350</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>13590955</v>
+      </c>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="9" t="n"/>
+      <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="9" t="n"/>
+      <c r="U9" s="9" t="n"/>
+      <c r="V9" s="9" t="n"/>
+      <c r="W9" s="9" t="n"/>
+      <c r="X9" s="9" t="n"/>
+      <c r="Y9" s="9" t="n"/>
+      <c r="Z9" s="9" t="n"/>
+      <c r="AA9" s="15">
+        <f>SUM(B9:Z9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜営業収入</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>11571200</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>12729500</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>10817650</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>7592596</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>12008250</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>14734304</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>14492300</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>9738050</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>12227100</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>7979350</v>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>13590955</v>
-      </c>
+          <t xml:space="preserve">  収入｜売掛金回収</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
@@ -1097,7 +1046,7 @@
       <c r="X10" s="9" t="n"/>
       <c r="Y10" s="9" t="n"/>
       <c r="Z10" s="9" t="n"/>
-      <c r="AA10" s="17">
+      <c r="AA10" s="15">
         <f>SUM(B10:Z10)</f>
         <v/>
       </c>
@@ -1105,7 +1054,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜売掛金回収</t>
+          <t xml:space="preserve">  収入｜受取手形期日入金</t>
         </is>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -1133,7 +1082,7 @@
       <c r="X11" s="9" t="n"/>
       <c r="Y11" s="9" t="n"/>
       <c r="Z11" s="9" t="n"/>
-      <c r="AA11" s="17">
+      <c r="AA11" s="15">
         <f>SUM(B11:Z11)</f>
         <v/>
       </c>
@@ -1141,7 +1090,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜受取手形期日入金</t>
+          <t xml:space="preserve">  収入｜手形割引</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -1169,7 +1118,7 @@
       <c r="X12" s="9" t="n"/>
       <c r="Y12" s="9" t="n"/>
       <c r="Z12" s="9" t="n"/>
-      <c r="AA12" s="17">
+      <c r="AA12" s="15">
         <f>SUM(B12:Z12)</f>
         <v/>
       </c>
@@ -1177,7 +1126,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜手形割引</t>
+          <t xml:space="preserve">  収入｜その他収入</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -1205,162 +1154,162 @@
       <c r="X13" s="9" t="n"/>
       <c r="Y13" s="9" t="n"/>
       <c r="Z13" s="9" t="n"/>
-      <c r="AA13" s="17">
+      <c r="AA13" s="15">
         <f>SUM(B13:Z13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入｜その他収入</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9" t="n"/>
-      <c r="O14" s="9" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
-      <c r="R14" s="9" t="n"/>
-      <c r="S14" s="9" t="n"/>
-      <c r="T14" s="9" t="n"/>
-      <c r="U14" s="9" t="n"/>
-      <c r="V14" s="9" t="n"/>
-      <c r="W14" s="9" t="n"/>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="9" t="n"/>
-      <c r="Z14" s="9" t="n"/>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入 計</t>
+        </is>
+      </c>
+      <c r="B14" s="17">
+        <f>SUM(B9:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
+        <f>SUM(C9:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>SUM(D9:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>SUM(E9:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>SUM(F9:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>SUM(G9:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>SUM(H9:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="17">
+        <f>SUM(I9:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="17">
+        <f>SUM(J9:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="17">
+        <f>SUM(K9:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="17">
+        <f>SUM(L9:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="17">
+        <f>SUM(M9:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="17">
+        <f>SUM(N9:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="17">
+        <f>SUM(O9:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="17">
+        <f>SUM(P9:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="17">
+        <f>SUM(Q9:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="17">
+        <f>SUM(R9:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="17">
+        <f>SUM(S9:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="17">
+        <f>SUM(T9:T13)</f>
+        <v/>
+      </c>
+      <c r="U14" s="17">
+        <f>SUM(U9:U13)</f>
+        <v/>
+      </c>
+      <c r="V14" s="17">
+        <f>SUM(V9:V13)</f>
+        <v/>
+      </c>
+      <c r="W14" s="17">
+        <f>SUM(W9:W13)</f>
+        <v/>
+      </c>
+      <c r="X14" s="17">
+        <f>SUM(X9:X13)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="17">
+        <f>SUM(Y9:Y13)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="17">
+        <f>SUM(Z9:Z13)</f>
+        <v/>
+      </c>
       <c r="AA14" s="17">
-        <f>SUM(B14:Z14)</f>
+        <f>SUM(AA9:AA13)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入 計</t>
-        </is>
-      </c>
-      <c r="B15" s="19">
-        <f>SUM(B10:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="19">
-        <f>SUM(C10:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="19">
-        <f>SUM(D10:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="19">
-        <f>SUM(E10:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="19">
-        <f>SUM(F10:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="19">
-        <f>SUM(G10:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="19">
-        <f>SUM(H10:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="19">
-        <f>SUM(I10:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="19">
-        <f>SUM(J10:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="19">
-        <f>SUM(K10:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="19">
-        <f>SUM(L10:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="19">
-        <f>SUM(M10:M14)</f>
-        <v/>
-      </c>
-      <c r="N15" s="19">
-        <f>SUM(N10:N14)</f>
-        <v/>
-      </c>
-      <c r="O15" s="19">
-        <f>SUM(O10:O14)</f>
-        <v/>
-      </c>
-      <c r="P15" s="19">
-        <f>SUM(P10:P14)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="19">
-        <f>SUM(Q10:Q14)</f>
-        <v/>
-      </c>
-      <c r="R15" s="19">
-        <f>SUM(R10:R14)</f>
-        <v/>
-      </c>
-      <c r="S15" s="19">
-        <f>SUM(S10:S14)</f>
-        <v/>
-      </c>
-      <c r="T15" s="19">
-        <f>SUM(T10:T14)</f>
-        <v/>
-      </c>
-      <c r="U15" s="19">
-        <f>SUM(U10:U14)</f>
-        <v/>
-      </c>
-      <c r="V15" s="19">
-        <f>SUM(V10:V14)</f>
-        <v/>
-      </c>
-      <c r="W15" s="19">
-        <f>SUM(W10:W14)</f>
-        <v/>
-      </c>
-      <c r="X15" s="19">
-        <f>SUM(X10:X14)</f>
-        <v/>
-      </c>
-      <c r="Y15" s="19">
-        <f>SUM(Y10:Y14)</f>
-        <v/>
-      </c>
-      <c r="Z15" s="19">
-        <f>SUM(Z10:Z14)</f>
-        <v/>
-      </c>
-      <c r="AA15" s="19">
-        <f>SUM(AA10:AA14)</f>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出｜現金仕入</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+      <c r="L15" s="9" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="9" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="9" t="n"/>
+      <c r="AA15" s="15">
+        <f>SUM(B15:Z15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜現金仕入</t>
+          <t xml:space="preserve">  支出｜買掛金支払</t>
         </is>
       </c>
       <c r="B16" s="9" t="n"/>
@@ -1388,7 +1337,7 @@
       <c r="X16" s="9" t="n"/>
       <c r="Y16" s="9" t="n"/>
       <c r="Z16" s="9" t="n"/>
-      <c r="AA16" s="17">
+      <c r="AA16" s="15">
         <f>SUM(B16:Z16)</f>
         <v/>
       </c>
@@ -1396,7 +1345,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜買掛金支払</t>
+          <t xml:space="preserve">  支出｜支払手形決済</t>
         </is>
       </c>
       <c r="B17" s="9" t="n"/>
@@ -1424,7 +1373,7 @@
       <c r="X17" s="9" t="n"/>
       <c r="Y17" s="9" t="n"/>
       <c r="Z17" s="9" t="n"/>
-      <c r="AA17" s="17">
+      <c r="AA17" s="15">
         <f>SUM(B17:Z17)</f>
         <v/>
       </c>
@@ -1432,7 +1381,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜支払手形決済</t>
+          <t xml:space="preserve">  支出｜未払金支払</t>
         </is>
       </c>
       <c r="B18" s="9" t="n"/>
@@ -1460,7 +1409,7 @@
       <c r="X18" s="9" t="n"/>
       <c r="Y18" s="9" t="n"/>
       <c r="Z18" s="9" t="n"/>
-      <c r="AA18" s="17">
+      <c r="AA18" s="15">
         <f>SUM(B18:Z18)</f>
         <v/>
       </c>
@@ -1468,7 +1417,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜未払金支払</t>
+          <t xml:space="preserve">  支出｜人件費（給与・賞与）</t>
         </is>
       </c>
       <c r="B19" s="9" t="n"/>
@@ -1496,7 +1445,7 @@
       <c r="X19" s="9" t="n"/>
       <c r="Y19" s="9" t="n"/>
       <c r="Z19" s="9" t="n"/>
-      <c r="AA19" s="17">
+      <c r="AA19" s="15">
         <f>SUM(B19:Z19)</f>
         <v/>
       </c>
@@ -1504,7 +1453,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜人件費（給与・賞与）</t>
+          <t xml:space="preserve">  支出｜法定福利費</t>
         </is>
       </c>
       <c r="B20" s="9" t="n"/>
@@ -1532,7 +1481,7 @@
       <c r="X20" s="9" t="n"/>
       <c r="Y20" s="9" t="n"/>
       <c r="Z20" s="9" t="n"/>
-      <c r="AA20" s="17">
+      <c r="AA20" s="15">
         <f>SUM(B20:Z20)</f>
         <v/>
       </c>
@@ -1540,7 +1489,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜法定福利費</t>
+          <t xml:space="preserve">  支出｜地代家賃</t>
         </is>
       </c>
       <c r="B21" s="9" t="n"/>
@@ -1568,7 +1517,7 @@
       <c r="X21" s="9" t="n"/>
       <c r="Y21" s="9" t="n"/>
       <c r="Z21" s="9" t="n"/>
-      <c r="AA21" s="17">
+      <c r="AA21" s="15">
         <f>SUM(B21:Z21)</f>
         <v/>
       </c>
@@ -1576,7 +1525,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜地代家賃</t>
+          <t xml:space="preserve">  支出｜水道光熱費・通信費</t>
         </is>
       </c>
       <c r="B22" s="9" t="n"/>
@@ -1604,7 +1553,7 @@
       <c r="X22" s="9" t="n"/>
       <c r="Y22" s="9" t="n"/>
       <c r="Z22" s="9" t="n"/>
-      <c r="AA22" s="17">
+      <c r="AA22" s="15">
         <f>SUM(B22:Z22)</f>
         <v/>
       </c>
@@ -1612,7 +1561,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜水道光熱費・通信費</t>
+          <t xml:space="preserve">  支出｜その他経費</t>
         </is>
       </c>
       <c r="B23" s="9" t="n"/>
@@ -1640,7 +1589,7 @@
       <c r="X23" s="9" t="n"/>
       <c r="Y23" s="9" t="n"/>
       <c r="Z23" s="9" t="n"/>
-      <c r="AA23" s="17">
+      <c r="AA23" s="15">
         <f>SUM(B23:Z23)</f>
         <v/>
       </c>
@@ -1648,7 +1597,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜その他経費</t>
+          <t xml:space="preserve">  支出｜支払利息・割引料</t>
         </is>
       </c>
       <c r="B24" s="9" t="n"/>
@@ -1676,306 +1625,306 @@
       <c r="X24" s="9" t="n"/>
       <c r="Y24" s="9" t="n"/>
       <c r="Z24" s="9" t="n"/>
-      <c r="AA24" s="17">
+      <c r="AA24" s="15">
         <f>SUM(B24:Z24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  支出｜支払利息・割引料</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
-      <c r="O25" s="9" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="9" t="n"/>
-      <c r="S25" s="9" t="n"/>
-      <c r="T25" s="9" t="n"/>
-      <c r="U25" s="9" t="n"/>
-      <c r="V25" s="9" t="n"/>
-      <c r="W25" s="9" t="n"/>
-      <c r="X25" s="9" t="n"/>
-      <c r="Y25" s="9" t="n"/>
-      <c r="Z25" s="9" t="n"/>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出 計</t>
+        </is>
+      </c>
+      <c r="B25" s="17">
+        <f>SUM(B15:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="17">
+        <f>SUM(C15:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>SUM(D15:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>SUM(E15:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>SUM(F15:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>SUM(G15:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>SUM(H15:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>SUM(I15:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>SUM(J15:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>SUM(K15:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="17">
+        <f>SUM(L15:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="17">
+        <f>SUM(M15:M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="17">
+        <f>SUM(N15:N24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="17">
+        <f>SUM(O15:O24)</f>
+        <v/>
+      </c>
+      <c r="P25" s="17">
+        <f>SUM(P15:P24)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="17">
+        <f>SUM(Q15:Q24)</f>
+        <v/>
+      </c>
+      <c r="R25" s="17">
+        <f>SUM(R15:R24)</f>
+        <v/>
+      </c>
+      <c r="S25" s="17">
+        <f>SUM(S15:S24)</f>
+        <v/>
+      </c>
+      <c r="T25" s="17">
+        <f>SUM(T15:T24)</f>
+        <v/>
+      </c>
+      <c r="U25" s="17">
+        <f>SUM(U15:U24)</f>
+        <v/>
+      </c>
+      <c r="V25" s="17">
+        <f>SUM(V15:V24)</f>
+        <v/>
+      </c>
+      <c r="W25" s="17">
+        <f>SUM(W15:W24)</f>
+        <v/>
+      </c>
+      <c r="X25" s="17">
+        <f>SUM(X15:X24)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="17">
+        <f>SUM(Y15:Y24)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="17">
+        <f>SUM(Z15:Z24)</f>
+        <v/>
+      </c>
       <c r="AA25" s="17">
-        <f>SUM(B25:Z25)</f>
+        <f>SUM(AA15:AA24)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出 計</t>
+          <t>経常収支 差額（収入－支出）</t>
         </is>
       </c>
       <c r="B26" s="19">
-        <f>SUM(B16:B25)</f>
+        <f>B14-B25</f>
         <v/>
       </c>
       <c r="C26" s="19">
-        <f>SUM(C16:C25)</f>
+        <f>C14-C25</f>
         <v/>
       </c>
       <c r="D26" s="19">
-        <f>SUM(D16:D25)</f>
+        <f>D14-D25</f>
         <v/>
       </c>
       <c r="E26" s="19">
-        <f>SUM(E16:E25)</f>
+        <f>E14-E25</f>
         <v/>
       </c>
       <c r="F26" s="19">
-        <f>SUM(F16:F25)</f>
+        <f>F14-F25</f>
         <v/>
       </c>
       <c r="G26" s="19">
-        <f>SUM(G16:G25)</f>
+        <f>G14-G25</f>
         <v/>
       </c>
       <c r="H26" s="19">
-        <f>SUM(H16:H25)</f>
+        <f>H14-H25</f>
         <v/>
       </c>
       <c r="I26" s="19">
-        <f>SUM(I16:I25)</f>
+        <f>I14-I25</f>
         <v/>
       </c>
       <c r="J26" s="19">
-        <f>SUM(J16:J25)</f>
+        <f>J14-J25</f>
         <v/>
       </c>
       <c r="K26" s="19">
-        <f>SUM(K16:K25)</f>
+        <f>K14-K25</f>
         <v/>
       </c>
       <c r="L26" s="19">
-        <f>SUM(L16:L25)</f>
+        <f>L14-L25</f>
         <v/>
       </c>
       <c r="M26" s="19">
-        <f>SUM(M16:M25)</f>
+        <f>M14-M25</f>
         <v/>
       </c>
       <c r="N26" s="19">
-        <f>SUM(N16:N25)</f>
+        <f>N14-N25</f>
         <v/>
       </c>
       <c r="O26" s="19">
-        <f>SUM(O16:O25)</f>
+        <f>O14-O25</f>
         <v/>
       </c>
       <c r="P26" s="19">
-        <f>SUM(P16:P25)</f>
+        <f>P14-P25</f>
         <v/>
       </c>
       <c r="Q26" s="19">
-        <f>SUM(Q16:Q25)</f>
+        <f>Q14-Q25</f>
         <v/>
       </c>
       <c r="R26" s="19">
-        <f>SUM(R16:R25)</f>
+        <f>R14-R25</f>
         <v/>
       </c>
       <c r="S26" s="19">
-        <f>SUM(S16:S25)</f>
+        <f>S14-S25</f>
         <v/>
       </c>
       <c r="T26" s="19">
-        <f>SUM(T16:T25)</f>
+        <f>T14-T25</f>
         <v/>
       </c>
       <c r="U26" s="19">
-        <f>SUM(U16:U25)</f>
+        <f>U14-U25</f>
         <v/>
       </c>
       <c r="V26" s="19">
-        <f>SUM(V16:V25)</f>
+        <f>V14-V25</f>
         <v/>
       </c>
       <c r="W26" s="19">
-        <f>SUM(W16:W25)</f>
+        <f>W14-W25</f>
         <v/>
       </c>
       <c r="X26" s="19">
-        <f>SUM(X16:X25)</f>
+        <f>X14-X25</f>
         <v/>
       </c>
       <c r="Y26" s="19">
-        <f>SUM(Y16:Y25)</f>
+        <f>Y14-Y25</f>
         <v/>
       </c>
       <c r="Z26" s="19">
-        <f>SUM(Z16:Z25)</f>
+        <f>Z14-Z25</f>
         <v/>
       </c>
       <c r="AA26" s="19">
-        <f>SUM(AA16:AA25)</f>
+        <f>AA14-AA25</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>経常収支 差額（収入－支出）</t>
-        </is>
-      </c>
-      <c r="B27" s="14">
-        <f>B15-B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="14">
-        <f>C15-C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="14">
-        <f>D15-D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
-        <f>E15-E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="14">
-        <f>F15-F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>G15-G26</f>
-        <v/>
-      </c>
-      <c r="H27" s="14">
-        <f>H15-H26</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>I15-I26</f>
-        <v/>
-      </c>
-      <c r="J27" s="14">
-        <f>J15-J26</f>
-        <v/>
-      </c>
-      <c r="K27" s="14">
-        <f>K15-K26</f>
-        <v/>
-      </c>
-      <c r="L27" s="14">
-        <f>L15-L26</f>
-        <v/>
-      </c>
-      <c r="M27" s="14">
-        <f>M15-M26</f>
-        <v/>
-      </c>
-      <c r="N27" s="14">
-        <f>N15-N26</f>
-        <v/>
-      </c>
-      <c r="O27" s="14">
-        <f>O15-O26</f>
-        <v/>
-      </c>
-      <c r="P27" s="14">
-        <f>P15-P26</f>
-        <v/>
-      </c>
-      <c r="Q27" s="14">
-        <f>Q15-Q26</f>
-        <v/>
-      </c>
-      <c r="R27" s="14">
-        <f>R15-R26</f>
-        <v/>
-      </c>
-      <c r="S27" s="14">
-        <f>S15-S26</f>
-        <v/>
-      </c>
-      <c r="T27" s="14">
-        <f>T15-T26</f>
-        <v/>
-      </c>
-      <c r="U27" s="14">
-        <f>U15-U26</f>
-        <v/>
-      </c>
-      <c r="V27" s="14">
-        <f>V15-V26</f>
-        <v/>
-      </c>
-      <c r="W27" s="14">
-        <f>W15-W26</f>
-        <v/>
-      </c>
-      <c r="X27" s="14">
-        <f>X15-X26</f>
-        <v/>
-      </c>
-      <c r="Y27" s="14">
-        <f>Y15-Y26</f>
-        <v/>
-      </c>
-      <c r="Z27" s="14">
-        <f>Z15-Z26</f>
-        <v/>
-      </c>
-      <c r="AA27" s="14">
-        <f>AA15-AA26</f>
-        <v/>
-      </c>
+          <t>経常外収支</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
+      <c r="N27" s="14" t="n"/>
+      <c r="O27" s="14" t="n"/>
+      <c r="P27" s="14" t="n"/>
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="14" t="n"/>
+      <c r="S27" s="14" t="n"/>
+      <c r="T27" s="14" t="n"/>
+      <c r="U27" s="14" t="n"/>
+      <c r="V27" s="14" t="n"/>
+      <c r="W27" s="14" t="n"/>
+      <c r="X27" s="14" t="n"/>
+      <c r="Y27" s="14" t="n"/>
+      <c r="Z27" s="14" t="n"/>
+      <c r="AA27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>経常外収支</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="16" t="n"/>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
-      <c r="M28" s="16" t="n"/>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="16" t="n"/>
-      <c r="P28" s="16" t="n"/>
-      <c r="Q28" s="16" t="n"/>
-      <c r="R28" s="16" t="n"/>
-      <c r="S28" s="16" t="n"/>
-      <c r="T28" s="16" t="n"/>
-      <c r="U28" s="16" t="n"/>
-      <c r="V28" s="16" t="n"/>
-      <c r="W28" s="16" t="n"/>
-      <c r="X28" s="16" t="n"/>
-      <c r="Y28" s="16" t="n"/>
-      <c r="Z28" s="16" t="n"/>
-      <c r="AA28" s="16" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入｜固定資産売却収入</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="9" t="n"/>
+      <c r="M28" s="9" t="n"/>
+      <c r="N28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
+      <c r="P28" s="9" t="n"/>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="9" t="n"/>
+      <c r="S28" s="9" t="n"/>
+      <c r="T28" s="9" t="n"/>
+      <c r="U28" s="9" t="n"/>
+      <c r="V28" s="9" t="n"/>
+      <c r="W28" s="9" t="n"/>
+      <c r="X28" s="9" t="n"/>
+      <c r="Y28" s="9" t="n"/>
+      <c r="Z28" s="9" t="n"/>
+      <c r="AA28" s="15">
+        <f>SUM(B28:Z28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜固定資産売却収入</t>
+          <t xml:space="preserve">  収入｜保険金・補助金等</t>
         </is>
       </c>
       <c r="B29" s="9" t="n"/>
@@ -2003,7 +1952,7 @@
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
-      <c r="AA29" s="17">
+      <c r="AA29" s="15">
         <f>SUM(B29:Z29)</f>
         <v/>
       </c>
@@ -2011,7 +1960,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜保険金・補助金等</t>
+          <t xml:space="preserve">  収入｜その他</t>
         </is>
       </c>
       <c r="B30" s="9" t="n"/>
@@ -2039,162 +1988,162 @@
       <c r="X30" s="9" t="n"/>
       <c r="Y30" s="9" t="n"/>
       <c r="Z30" s="9" t="n"/>
-      <c r="AA30" s="17">
+      <c r="AA30" s="15">
         <f>SUM(B30:Z30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入｜その他</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="9" t="n"/>
-      <c r="N31" s="9" t="n"/>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="9" t="n"/>
-      <c r="S31" s="9" t="n"/>
-      <c r="T31" s="9" t="n"/>
-      <c r="U31" s="9" t="n"/>
-      <c r="V31" s="9" t="n"/>
-      <c r="W31" s="9" t="n"/>
-      <c r="X31" s="9" t="n"/>
-      <c r="Y31" s="9" t="n"/>
-      <c r="Z31" s="9" t="n"/>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入 計</t>
+        </is>
+      </c>
+      <c r="B31" s="17">
+        <f>SUM(B28:B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="17">
+        <f>SUM(C28:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>SUM(D28:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="17">
+        <f>SUM(E28:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="17">
+        <f>SUM(F28:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="17">
+        <f>SUM(G28:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>SUM(H28:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>SUM(I28:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="17">
+        <f>SUM(J28:J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="17">
+        <f>SUM(K28:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="17">
+        <f>SUM(L28:L30)</f>
+        <v/>
+      </c>
+      <c r="M31" s="17">
+        <f>SUM(M28:M30)</f>
+        <v/>
+      </c>
+      <c r="N31" s="17">
+        <f>SUM(N28:N30)</f>
+        <v/>
+      </c>
+      <c r="O31" s="17">
+        <f>SUM(O28:O30)</f>
+        <v/>
+      </c>
+      <c r="P31" s="17">
+        <f>SUM(P28:P30)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="17">
+        <f>SUM(Q28:Q30)</f>
+        <v/>
+      </c>
+      <c r="R31" s="17">
+        <f>SUM(R28:R30)</f>
+        <v/>
+      </c>
+      <c r="S31" s="17">
+        <f>SUM(S28:S30)</f>
+        <v/>
+      </c>
+      <c r="T31" s="17">
+        <f>SUM(T28:T30)</f>
+        <v/>
+      </c>
+      <c r="U31" s="17">
+        <f>SUM(U28:U30)</f>
+        <v/>
+      </c>
+      <c r="V31" s="17">
+        <f>SUM(V28:V30)</f>
+        <v/>
+      </c>
+      <c r="W31" s="17">
+        <f>SUM(W28:W30)</f>
+        <v/>
+      </c>
+      <c r="X31" s="17">
+        <f>SUM(X28:X30)</f>
+        <v/>
+      </c>
+      <c r="Y31" s="17">
+        <f>SUM(Y28:Y30)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="17">
+        <f>SUM(Z28:Z30)</f>
+        <v/>
+      </c>
       <c r="AA31" s="17">
-        <f>SUM(B31:Z31)</f>
+        <f>SUM(AA28:AA30)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入 計</t>
-        </is>
-      </c>
-      <c r="B32" s="19">
-        <f>SUM(B29:B31)</f>
-        <v/>
-      </c>
-      <c r="C32" s="19">
-        <f>SUM(C29:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="19">
-        <f>SUM(D29:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="19">
-        <f>SUM(E29:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="19">
-        <f>SUM(F29:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="19">
-        <f>SUM(G29:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="19">
-        <f>SUM(H29:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="19">
-        <f>SUM(I29:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="19">
-        <f>SUM(J29:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="19">
-        <f>SUM(K29:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="19">
-        <f>SUM(L29:L31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="19">
-        <f>SUM(M29:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="19">
-        <f>SUM(N29:N31)</f>
-        <v/>
-      </c>
-      <c r="O32" s="19">
-        <f>SUM(O29:O31)</f>
-        <v/>
-      </c>
-      <c r="P32" s="19">
-        <f>SUM(P29:P31)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="19">
-        <f>SUM(Q29:Q31)</f>
-        <v/>
-      </c>
-      <c r="R32" s="19">
-        <f>SUM(R29:R31)</f>
-        <v/>
-      </c>
-      <c r="S32" s="19">
-        <f>SUM(S29:S31)</f>
-        <v/>
-      </c>
-      <c r="T32" s="19">
-        <f>SUM(T29:T31)</f>
-        <v/>
-      </c>
-      <c r="U32" s="19">
-        <f>SUM(U29:U31)</f>
-        <v/>
-      </c>
-      <c r="V32" s="19">
-        <f>SUM(V29:V31)</f>
-        <v/>
-      </c>
-      <c r="W32" s="19">
-        <f>SUM(W29:W31)</f>
-        <v/>
-      </c>
-      <c r="X32" s="19">
-        <f>SUM(X29:X31)</f>
-        <v/>
-      </c>
-      <c r="Y32" s="19">
-        <f>SUM(Y29:Y31)</f>
-        <v/>
-      </c>
-      <c r="Z32" s="19">
-        <f>SUM(Z29:Z31)</f>
-        <v/>
-      </c>
-      <c r="AA32" s="19">
-        <f>SUM(AA29:AA31)</f>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出｜設備投資（固定資産購入）</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="9" t="n"/>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
+      <c r="P32" s="9" t="n"/>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="9" t="n"/>
+      <c r="S32" s="9" t="n"/>
+      <c r="T32" s="9" t="n"/>
+      <c r="U32" s="9" t="n"/>
+      <c r="V32" s="9" t="n"/>
+      <c r="W32" s="9" t="n"/>
+      <c r="X32" s="9" t="n"/>
+      <c r="Y32" s="9" t="n"/>
+      <c r="Z32" s="9" t="n"/>
+      <c r="AA32" s="15">
+        <f>SUM(B32:Z32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜設備投資（固定資産購入）</t>
+          <t xml:space="preserve">  支出｜法人税・消費税等納付</t>
         </is>
       </c>
       <c r="B33" s="9" t="n"/>
@@ -2222,7 +2171,7 @@
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
       <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="17">
+      <c r="AA33" s="15">
         <f>SUM(B33:Z33)</f>
         <v/>
       </c>
@@ -2230,7 +2179,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜法人税・消費税等納付</t>
+          <t xml:space="preserve">  支出｜その他</t>
         </is>
       </c>
       <c r="B34" s="9" t="n"/>
@@ -2258,306 +2207,306 @@
       <c r="X34" s="9" t="n"/>
       <c r="Y34" s="9" t="n"/>
       <c r="Z34" s="9" t="n"/>
-      <c r="AA34" s="17">
+      <c r="AA34" s="15">
         <f>SUM(B34:Z34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  支出｜その他</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="9" t="n"/>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="9" t="n"/>
-      <c r="O35" s="9" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n"/>
-      <c r="T35" s="9" t="n"/>
-      <c r="U35" s="9" t="n"/>
-      <c r="V35" s="9" t="n"/>
-      <c r="W35" s="9" t="n"/>
-      <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
-      <c r="Z35" s="9" t="n"/>
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出 計</t>
+        </is>
+      </c>
+      <c r="B35" s="17">
+        <f>SUM(B32:B34)</f>
+        <v/>
+      </c>
+      <c r="C35" s="17">
+        <f>SUM(C32:C34)</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>SUM(D32:D34)</f>
+        <v/>
+      </c>
+      <c r="E35" s="17">
+        <f>SUM(E32:E34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>SUM(F32:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>SUM(G32:G34)</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>SUM(H32:H34)</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>SUM(I32:I34)</f>
+        <v/>
+      </c>
+      <c r="J35" s="17">
+        <f>SUM(J32:J34)</f>
+        <v/>
+      </c>
+      <c r="K35" s="17">
+        <f>SUM(K32:K34)</f>
+        <v/>
+      </c>
+      <c r="L35" s="17">
+        <f>SUM(L32:L34)</f>
+        <v/>
+      </c>
+      <c r="M35" s="17">
+        <f>SUM(M32:M34)</f>
+        <v/>
+      </c>
+      <c r="N35" s="17">
+        <f>SUM(N32:N34)</f>
+        <v/>
+      </c>
+      <c r="O35" s="17">
+        <f>SUM(O32:O34)</f>
+        <v/>
+      </c>
+      <c r="P35" s="17">
+        <f>SUM(P32:P34)</f>
+        <v/>
+      </c>
+      <c r="Q35" s="17">
+        <f>SUM(Q32:Q34)</f>
+        <v/>
+      </c>
+      <c r="R35" s="17">
+        <f>SUM(R32:R34)</f>
+        <v/>
+      </c>
+      <c r="S35" s="17">
+        <f>SUM(S32:S34)</f>
+        <v/>
+      </c>
+      <c r="T35" s="17">
+        <f>SUM(T32:T34)</f>
+        <v/>
+      </c>
+      <c r="U35" s="17">
+        <f>SUM(U32:U34)</f>
+        <v/>
+      </c>
+      <c r="V35" s="17">
+        <f>SUM(V32:V34)</f>
+        <v/>
+      </c>
+      <c r="W35" s="17">
+        <f>SUM(W32:W34)</f>
+        <v/>
+      </c>
+      <c r="X35" s="17">
+        <f>SUM(X32:X34)</f>
+        <v/>
+      </c>
+      <c r="Y35" s="17">
+        <f>SUM(Y32:Y34)</f>
+        <v/>
+      </c>
+      <c r="Z35" s="17">
+        <f>SUM(Z32:Z34)</f>
+        <v/>
+      </c>
       <c r="AA35" s="17">
-        <f>SUM(B35:Z35)</f>
+        <f>SUM(AA32:AA34)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出 計</t>
+          <t>経常外収支 差額（収入－支出）</t>
         </is>
       </c>
       <c r="B36" s="19">
-        <f>SUM(B33:B35)</f>
+        <f>B31-B35</f>
         <v/>
       </c>
       <c r="C36" s="19">
-        <f>SUM(C33:C35)</f>
+        <f>C31-C35</f>
         <v/>
       </c>
       <c r="D36" s="19">
-        <f>SUM(D33:D35)</f>
+        <f>D31-D35</f>
         <v/>
       </c>
       <c r="E36" s="19">
-        <f>SUM(E33:E35)</f>
+        <f>E31-E35</f>
         <v/>
       </c>
       <c r="F36" s="19">
-        <f>SUM(F33:F35)</f>
+        <f>F31-F35</f>
         <v/>
       </c>
       <c r="G36" s="19">
-        <f>SUM(G33:G35)</f>
+        <f>G31-G35</f>
         <v/>
       </c>
       <c r="H36" s="19">
-        <f>SUM(H33:H35)</f>
+        <f>H31-H35</f>
         <v/>
       </c>
       <c r="I36" s="19">
-        <f>SUM(I33:I35)</f>
+        <f>I31-I35</f>
         <v/>
       </c>
       <c r="J36" s="19">
-        <f>SUM(J33:J35)</f>
+        <f>J31-J35</f>
         <v/>
       </c>
       <c r="K36" s="19">
-        <f>SUM(K33:K35)</f>
+        <f>K31-K35</f>
         <v/>
       </c>
       <c r="L36" s="19">
-        <f>SUM(L33:L35)</f>
+        <f>L31-L35</f>
         <v/>
       </c>
       <c r="M36" s="19">
-        <f>SUM(M33:M35)</f>
+        <f>M31-M35</f>
         <v/>
       </c>
       <c r="N36" s="19">
-        <f>SUM(N33:N35)</f>
+        <f>N31-N35</f>
         <v/>
       </c>
       <c r="O36" s="19">
-        <f>SUM(O33:O35)</f>
+        <f>O31-O35</f>
         <v/>
       </c>
       <c r="P36" s="19">
-        <f>SUM(P33:P35)</f>
+        <f>P31-P35</f>
         <v/>
       </c>
       <c r="Q36" s="19">
-        <f>SUM(Q33:Q35)</f>
+        <f>Q31-Q35</f>
         <v/>
       </c>
       <c r="R36" s="19">
-        <f>SUM(R33:R35)</f>
+        <f>R31-R35</f>
         <v/>
       </c>
       <c r="S36" s="19">
-        <f>SUM(S33:S35)</f>
+        <f>S31-S35</f>
         <v/>
       </c>
       <c r="T36" s="19">
-        <f>SUM(T33:T35)</f>
+        <f>T31-T35</f>
         <v/>
       </c>
       <c r="U36" s="19">
-        <f>SUM(U33:U35)</f>
+        <f>U31-U35</f>
         <v/>
       </c>
       <c r="V36" s="19">
-        <f>SUM(V33:V35)</f>
+        <f>V31-V35</f>
         <v/>
       </c>
       <c r="W36" s="19">
-        <f>SUM(W33:W35)</f>
+        <f>W31-W35</f>
         <v/>
       </c>
       <c r="X36" s="19">
-        <f>SUM(X33:X35)</f>
+        <f>X31-X35</f>
         <v/>
       </c>
       <c r="Y36" s="19">
-        <f>SUM(Y33:Y35)</f>
+        <f>Y31-Y35</f>
         <v/>
       </c>
       <c r="Z36" s="19">
-        <f>SUM(Z33:Z35)</f>
+        <f>Z31-Z35</f>
         <v/>
       </c>
       <c r="AA36" s="19">
-        <f>SUM(AA33:AA35)</f>
+        <f>AA31-AA35</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>経常外収支 差額（収入－支出）</t>
-        </is>
-      </c>
-      <c r="B37" s="14">
-        <f>B32-B36</f>
-        <v/>
-      </c>
-      <c r="C37" s="14">
-        <f>C32-C36</f>
-        <v/>
-      </c>
-      <c r="D37" s="14">
-        <f>D32-D36</f>
-        <v/>
-      </c>
-      <c r="E37" s="14">
-        <f>E32-E36</f>
-        <v/>
-      </c>
-      <c r="F37" s="14">
-        <f>F32-F36</f>
-        <v/>
-      </c>
-      <c r="G37" s="14">
-        <f>G32-G36</f>
-        <v/>
-      </c>
-      <c r="H37" s="14">
-        <f>H32-H36</f>
-        <v/>
-      </c>
-      <c r="I37" s="14">
-        <f>I32-I36</f>
-        <v/>
-      </c>
-      <c r="J37" s="14">
-        <f>J32-J36</f>
-        <v/>
-      </c>
-      <c r="K37" s="14">
-        <f>K32-K36</f>
-        <v/>
-      </c>
-      <c r="L37" s="14">
-        <f>L32-L36</f>
-        <v/>
-      </c>
-      <c r="M37" s="14">
-        <f>M32-M36</f>
-        <v/>
-      </c>
-      <c r="N37" s="14">
-        <f>N32-N36</f>
-        <v/>
-      </c>
-      <c r="O37" s="14">
-        <f>O32-O36</f>
-        <v/>
-      </c>
-      <c r="P37" s="14">
-        <f>P32-P36</f>
-        <v/>
-      </c>
-      <c r="Q37" s="14">
-        <f>Q32-Q36</f>
-        <v/>
-      </c>
-      <c r="R37" s="14">
-        <f>R32-R36</f>
-        <v/>
-      </c>
-      <c r="S37" s="14">
-        <f>S32-S36</f>
-        <v/>
-      </c>
-      <c r="T37" s="14">
-        <f>T32-T36</f>
-        <v/>
-      </c>
-      <c r="U37" s="14">
-        <f>U32-U36</f>
-        <v/>
-      </c>
-      <c r="V37" s="14">
-        <f>V32-V36</f>
-        <v/>
-      </c>
-      <c r="W37" s="14">
-        <f>W32-W36</f>
-        <v/>
-      </c>
-      <c r="X37" s="14">
-        <f>X32-X36</f>
-        <v/>
-      </c>
-      <c r="Y37" s="14">
-        <f>Y32-Y36</f>
-        <v/>
-      </c>
-      <c r="Z37" s="14">
-        <f>Z32-Z36</f>
-        <v/>
-      </c>
-      <c r="AA37" s="14">
-        <f>AA32-AA36</f>
-        <v/>
-      </c>
+          <t>財務収支</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="14" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
+      <c r="N37" s="14" t="n"/>
+      <c r="O37" s="14" t="n"/>
+      <c r="P37" s="14" t="n"/>
+      <c r="Q37" s="14" t="n"/>
+      <c r="R37" s="14" t="n"/>
+      <c r="S37" s="14" t="n"/>
+      <c r="T37" s="14" t="n"/>
+      <c r="U37" s="14" t="n"/>
+      <c r="V37" s="14" t="n"/>
+      <c r="W37" s="14" t="n"/>
+      <c r="X37" s="14" t="n"/>
+      <c r="Y37" s="14" t="n"/>
+      <c r="Z37" s="14" t="n"/>
+      <c r="AA37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>財務収支</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="16" t="n"/>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
-      <c r="M38" s="16" t="n"/>
-      <c r="N38" s="16" t="n"/>
-      <c r="O38" s="16" t="n"/>
-      <c r="P38" s="16" t="n"/>
-      <c r="Q38" s="16" t="n"/>
-      <c r="R38" s="16" t="n"/>
-      <c r="S38" s="16" t="n"/>
-      <c r="T38" s="16" t="n"/>
-      <c r="U38" s="16" t="n"/>
-      <c r="V38" s="16" t="n"/>
-      <c r="W38" s="16" t="n"/>
-      <c r="X38" s="16" t="n"/>
-      <c r="Y38" s="16" t="n"/>
-      <c r="Z38" s="16" t="n"/>
-      <c r="AA38" s="16" t="n"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入｜借入金</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="9" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="9" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="9" t="n"/>
+      <c r="S38" s="9" t="n"/>
+      <c r="T38" s="9" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="9" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="9" t="n"/>
+      <c r="Y38" s="9" t="n"/>
+      <c r="Z38" s="9" t="n"/>
+      <c r="AA38" s="15">
+        <f>SUM(B38:Z38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜借入金</t>
+          <t xml:space="preserve">  収入｜増資・出資</t>
         </is>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -2585,7 +2534,7 @@
       <c r="X39" s="9" t="n"/>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
-      <c r="AA39" s="17">
+      <c r="AA39" s="15">
         <f>SUM(B39:Z39)</f>
         <v/>
       </c>
@@ -2593,7 +2542,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜増資・出資</t>
+          <t xml:space="preserve">  収入｜その他</t>
         </is>
       </c>
       <c r="B40" s="9" t="n"/>
@@ -2621,162 +2570,162 @@
       <c r="X40" s="9" t="n"/>
       <c r="Y40" s="9" t="n"/>
       <c r="Z40" s="9" t="n"/>
-      <c r="AA40" s="17">
+      <c r="AA40" s="15">
         <f>SUM(B40:Z40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入｜その他</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="9" t="n"/>
-      <c r="M41" s="9" t="n"/>
-      <c r="N41" s="9" t="n"/>
-      <c r="O41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n"/>
-      <c r="T41" s="9" t="n"/>
-      <c r="U41" s="9" t="n"/>
-      <c r="V41" s="9" t="n"/>
-      <c r="W41" s="9" t="n"/>
-      <c r="X41" s="9" t="n"/>
-      <c r="Y41" s="9" t="n"/>
-      <c r="Z41" s="9" t="n"/>
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入 計</t>
+        </is>
+      </c>
+      <c r="B41" s="17">
+        <f>SUM(B38:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="17">
+        <f>SUM(C38:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>SUM(D38:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>SUM(E38:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>SUM(F38:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>SUM(G38:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>SUM(H38:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="17">
+        <f>SUM(I38:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="17">
+        <f>SUM(J38:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="17">
+        <f>SUM(K38:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="17">
+        <f>SUM(L38:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="17">
+        <f>SUM(M38:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="17">
+        <f>SUM(N38:N40)</f>
+        <v/>
+      </c>
+      <c r="O41" s="17">
+        <f>SUM(O38:O40)</f>
+        <v/>
+      </c>
+      <c r="P41" s="17">
+        <f>SUM(P38:P40)</f>
+        <v/>
+      </c>
+      <c r="Q41" s="17">
+        <f>SUM(Q38:Q40)</f>
+        <v/>
+      </c>
+      <c r="R41" s="17">
+        <f>SUM(R38:R40)</f>
+        <v/>
+      </c>
+      <c r="S41" s="17">
+        <f>SUM(S38:S40)</f>
+        <v/>
+      </c>
+      <c r="T41" s="17">
+        <f>SUM(T38:T40)</f>
+        <v/>
+      </c>
+      <c r="U41" s="17">
+        <f>SUM(U38:U40)</f>
+        <v/>
+      </c>
+      <c r="V41" s="17">
+        <f>SUM(V38:V40)</f>
+        <v/>
+      </c>
+      <c r="W41" s="17">
+        <f>SUM(W38:W40)</f>
+        <v/>
+      </c>
+      <c r="X41" s="17">
+        <f>SUM(X38:X40)</f>
+        <v/>
+      </c>
+      <c r="Y41" s="17">
+        <f>SUM(Y38:Y40)</f>
+        <v/>
+      </c>
+      <c r="Z41" s="17">
+        <f>SUM(Z38:Z40)</f>
+        <v/>
+      </c>
       <c r="AA41" s="17">
-        <f>SUM(B41:Z41)</f>
+        <f>SUM(AA38:AA40)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入 計</t>
-        </is>
-      </c>
-      <c r="B42" s="19">
-        <f>SUM(B39:B41)</f>
-        <v/>
-      </c>
-      <c r="C42" s="19">
-        <f>SUM(C39:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="19">
-        <f>SUM(D39:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="19">
-        <f>SUM(E39:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="19">
-        <f>SUM(F39:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="19">
-        <f>SUM(G39:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="19">
-        <f>SUM(H39:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="19">
-        <f>SUM(I39:I41)</f>
-        <v/>
-      </c>
-      <c r="J42" s="19">
-        <f>SUM(J39:J41)</f>
-        <v/>
-      </c>
-      <c r="K42" s="19">
-        <f>SUM(K39:K41)</f>
-        <v/>
-      </c>
-      <c r="L42" s="19">
-        <f>SUM(L39:L41)</f>
-        <v/>
-      </c>
-      <c r="M42" s="19">
-        <f>SUM(M39:M41)</f>
-        <v/>
-      </c>
-      <c r="N42" s="19">
-        <f>SUM(N39:N41)</f>
-        <v/>
-      </c>
-      <c r="O42" s="19">
-        <f>SUM(O39:O41)</f>
-        <v/>
-      </c>
-      <c r="P42" s="19">
-        <f>SUM(P39:P41)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="19">
-        <f>SUM(Q39:Q41)</f>
-        <v/>
-      </c>
-      <c r="R42" s="19">
-        <f>SUM(R39:R41)</f>
-        <v/>
-      </c>
-      <c r="S42" s="19">
-        <f>SUM(S39:S41)</f>
-        <v/>
-      </c>
-      <c r="T42" s="19">
-        <f>SUM(T39:T41)</f>
-        <v/>
-      </c>
-      <c r="U42" s="19">
-        <f>SUM(U39:U41)</f>
-        <v/>
-      </c>
-      <c r="V42" s="19">
-        <f>SUM(V39:V41)</f>
-        <v/>
-      </c>
-      <c r="W42" s="19">
-        <f>SUM(W39:W41)</f>
-        <v/>
-      </c>
-      <c r="X42" s="19">
-        <f>SUM(X39:X41)</f>
-        <v/>
-      </c>
-      <c r="Y42" s="19">
-        <f>SUM(Y39:Y41)</f>
-        <v/>
-      </c>
-      <c r="Z42" s="19">
-        <f>SUM(Z39:Z41)</f>
-        <v/>
-      </c>
-      <c r="AA42" s="19">
-        <f>SUM(AA39:AA41)</f>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出｜借入金返済</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="9" t="n"/>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
+      <c r="P42" s="9" t="n"/>
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="9" t="n"/>
+      <c r="S42" s="9" t="n"/>
+      <c r="T42" s="9" t="n"/>
+      <c r="U42" s="9" t="n"/>
+      <c r="V42" s="9" t="n"/>
+      <c r="W42" s="9" t="n"/>
+      <c r="X42" s="9" t="n"/>
+      <c r="Y42" s="9" t="n"/>
+      <c r="Z42" s="9" t="n"/>
+      <c r="AA42" s="15">
+        <f>SUM(B42:Z42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜借入金返済</t>
+          <t xml:space="preserve">  支出｜配当金・役員借入返済</t>
         </is>
       </c>
       <c r="B43" s="9" t="n"/>
@@ -2804,7 +2753,7 @@
       <c r="X43" s="9" t="n"/>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
-      <c r="AA43" s="17">
+      <c r="AA43" s="15">
         <f>SUM(B43:Z43)</f>
         <v/>
       </c>
@@ -2812,7 +2761,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜配当金・役員借入返済</t>
+          <t xml:space="preserve">  支出｜その他</t>
         </is>
       </c>
       <c r="B44" s="9" t="n"/>
@@ -2840,266 +2789,338 @@
       <c r="X44" s="9" t="n"/>
       <c r="Y44" s="9" t="n"/>
       <c r="Z44" s="9" t="n"/>
-      <c r="AA44" s="17">
+      <c r="AA44" s="15">
         <f>SUM(B44:Z44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  支出｜その他</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
-      <c r="L45" s="9" t="n"/>
-      <c r="M45" s="9" t="n"/>
-      <c r="N45" s="9" t="n"/>
-      <c r="O45" s="9" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
-      <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n"/>
-      <c r="T45" s="9" t="n"/>
-      <c r="U45" s="9" t="n"/>
-      <c r="V45" s="9" t="n"/>
-      <c r="W45" s="9" t="n"/>
-      <c r="X45" s="9" t="n"/>
-      <c r="Y45" s="9" t="n"/>
-      <c r="Z45" s="9" t="n"/>
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出 計</t>
+        </is>
+      </c>
+      <c r="B45" s="17">
+        <f>SUM(B42:B44)</f>
+        <v/>
+      </c>
+      <c r="C45" s="17">
+        <f>SUM(C42:C44)</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>SUM(D42:D44)</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f>SUM(E42:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>SUM(F42:F44)</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>SUM(G42:G44)</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>SUM(H42:H44)</f>
+        <v/>
+      </c>
+      <c r="I45" s="17">
+        <f>SUM(I42:I44)</f>
+        <v/>
+      </c>
+      <c r="J45" s="17">
+        <f>SUM(J42:J44)</f>
+        <v/>
+      </c>
+      <c r="K45" s="17">
+        <f>SUM(K42:K44)</f>
+        <v/>
+      </c>
+      <c r="L45" s="17">
+        <f>SUM(L42:L44)</f>
+        <v/>
+      </c>
+      <c r="M45" s="17">
+        <f>SUM(M42:M44)</f>
+        <v/>
+      </c>
+      <c r="N45" s="17">
+        <f>SUM(N42:N44)</f>
+        <v/>
+      </c>
+      <c r="O45" s="17">
+        <f>SUM(O42:O44)</f>
+        <v/>
+      </c>
+      <c r="P45" s="17">
+        <f>SUM(P42:P44)</f>
+        <v/>
+      </c>
+      <c r="Q45" s="17">
+        <f>SUM(Q42:Q44)</f>
+        <v/>
+      </c>
+      <c r="R45" s="17">
+        <f>SUM(R42:R44)</f>
+        <v/>
+      </c>
+      <c r="S45" s="17">
+        <f>SUM(S42:S44)</f>
+        <v/>
+      </c>
+      <c r="T45" s="17">
+        <f>SUM(T42:T44)</f>
+        <v/>
+      </c>
+      <c r="U45" s="17">
+        <f>SUM(U42:U44)</f>
+        <v/>
+      </c>
+      <c r="V45" s="17">
+        <f>SUM(V42:V44)</f>
+        <v/>
+      </c>
+      <c r="W45" s="17">
+        <f>SUM(W42:W44)</f>
+        <v/>
+      </c>
+      <c r="X45" s="17">
+        <f>SUM(X42:X44)</f>
+        <v/>
+      </c>
+      <c r="Y45" s="17">
+        <f>SUM(Y42:Y44)</f>
+        <v/>
+      </c>
+      <c r="Z45" s="17">
+        <f>SUM(Z42:Z44)</f>
+        <v/>
+      </c>
       <c r="AA45" s="17">
-        <f>SUM(B45:Z45)</f>
+        <f>SUM(AA42:AA44)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出 計</t>
+          <t>財務収支 差額（収入－支出）</t>
         </is>
       </c>
       <c r="B46" s="19">
-        <f>SUM(B43:B45)</f>
+        <f>B41-B45</f>
         <v/>
       </c>
       <c r="C46" s="19">
-        <f>SUM(C43:C45)</f>
+        <f>C41-C45</f>
         <v/>
       </c>
       <c r="D46" s="19">
-        <f>SUM(D43:D45)</f>
+        <f>D41-D45</f>
         <v/>
       </c>
       <c r="E46" s="19">
-        <f>SUM(E43:E45)</f>
+        <f>E41-E45</f>
         <v/>
       </c>
       <c r="F46" s="19">
-        <f>SUM(F43:F45)</f>
+        <f>F41-F45</f>
         <v/>
       </c>
       <c r="G46" s="19">
-        <f>SUM(G43:G45)</f>
+        <f>G41-G45</f>
         <v/>
       </c>
       <c r="H46" s="19">
-        <f>SUM(H43:H45)</f>
+        <f>H41-H45</f>
         <v/>
       </c>
       <c r="I46" s="19">
-        <f>SUM(I43:I45)</f>
+        <f>I41-I45</f>
         <v/>
       </c>
       <c r="J46" s="19">
-        <f>SUM(J43:J45)</f>
+        <f>J41-J45</f>
         <v/>
       </c>
       <c r="K46" s="19">
-        <f>SUM(K43:K45)</f>
+        <f>K41-K45</f>
         <v/>
       </c>
       <c r="L46" s="19">
-        <f>SUM(L43:L45)</f>
+        <f>L41-L45</f>
         <v/>
       </c>
       <c r="M46" s="19">
-        <f>SUM(M43:M45)</f>
+        <f>M41-M45</f>
         <v/>
       </c>
       <c r="N46" s="19">
-        <f>SUM(N43:N45)</f>
+        <f>N41-N45</f>
         <v/>
       </c>
       <c r="O46" s="19">
-        <f>SUM(O43:O45)</f>
+        <f>O41-O45</f>
         <v/>
       </c>
       <c r="P46" s="19">
-        <f>SUM(P43:P45)</f>
+        <f>P41-P45</f>
         <v/>
       </c>
       <c r="Q46" s="19">
-        <f>SUM(Q43:Q45)</f>
+        <f>Q41-Q45</f>
         <v/>
       </c>
       <c r="R46" s="19">
-        <f>SUM(R43:R45)</f>
+        <f>R41-R45</f>
         <v/>
       </c>
       <c r="S46" s="19">
-        <f>SUM(S43:S45)</f>
+        <f>S41-S45</f>
         <v/>
       </c>
       <c r="T46" s="19">
-        <f>SUM(T43:T45)</f>
+        <f>T41-T45</f>
         <v/>
       </c>
       <c r="U46" s="19">
-        <f>SUM(U43:U45)</f>
+        <f>U41-U45</f>
         <v/>
       </c>
       <c r="V46" s="19">
-        <f>SUM(V43:V45)</f>
+        <f>V41-V45</f>
         <v/>
       </c>
       <c r="W46" s="19">
-        <f>SUM(W43:W45)</f>
+        <f>W41-W45</f>
         <v/>
       </c>
       <c r="X46" s="19">
-        <f>SUM(X43:X45)</f>
+        <f>X41-X45</f>
         <v/>
       </c>
       <c r="Y46" s="19">
-        <f>SUM(Y43:Y45)</f>
+        <f>Y41-Y45</f>
         <v/>
       </c>
       <c r="Z46" s="19">
-        <f>SUM(Z43:Z45)</f>
+        <f>Z41-Z45</f>
         <v/>
       </c>
       <c r="AA46" s="19">
-        <f>SUM(AA43:AA45)</f>
+        <f>AA41-AA45</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>財務収支 差額（収入－支出）</t>
-        </is>
-      </c>
-      <c r="B47" s="14">
-        <f>B42-B46</f>
-        <v/>
-      </c>
-      <c r="C47" s="14">
-        <f>C42-C46</f>
-        <v/>
-      </c>
-      <c r="D47" s="14">
-        <f>D42-D46</f>
-        <v/>
-      </c>
-      <c r="E47" s="14">
-        <f>E42-E46</f>
-        <v/>
-      </c>
-      <c r="F47" s="14">
-        <f>F42-F46</f>
-        <v/>
-      </c>
-      <c r="G47" s="14">
-        <f>G42-G46</f>
-        <v/>
-      </c>
-      <c r="H47" s="14">
-        <f>H42-H46</f>
-        <v/>
-      </c>
-      <c r="I47" s="14">
-        <f>I42-I46</f>
-        <v/>
-      </c>
-      <c r="J47" s="14">
-        <f>J42-J46</f>
-        <v/>
-      </c>
-      <c r="K47" s="14">
-        <f>K42-K46</f>
-        <v/>
-      </c>
-      <c r="L47" s="14">
-        <f>L42-L46</f>
-        <v/>
-      </c>
-      <c r="M47" s="14">
-        <f>M42-M46</f>
-        <v/>
-      </c>
-      <c r="N47" s="14">
-        <f>N42-N46</f>
-        <v/>
-      </c>
-      <c r="O47" s="14">
-        <f>O42-O46</f>
-        <v/>
-      </c>
-      <c r="P47" s="14">
-        <f>P42-P46</f>
-        <v/>
-      </c>
-      <c r="Q47" s="14">
-        <f>Q42-Q46</f>
-        <v/>
-      </c>
-      <c r="R47" s="14">
-        <f>R42-R46</f>
-        <v/>
-      </c>
-      <c r="S47" s="14">
-        <f>S42-S46</f>
-        <v/>
-      </c>
-      <c r="T47" s="14">
-        <f>T42-T46</f>
-        <v/>
-      </c>
-      <c r="U47" s="14">
-        <f>U42-U46</f>
-        <v/>
-      </c>
-      <c r="V47" s="14">
-        <f>V42-V46</f>
-        <v/>
-      </c>
-      <c r="W47" s="14">
-        <f>W42-W46</f>
-        <v/>
-      </c>
-      <c r="X47" s="14">
-        <f>X42-X46</f>
-        <v/>
-      </c>
-      <c r="Y47" s="14">
-        <f>Y42-Y46</f>
-        <v/>
-      </c>
-      <c r="Z47" s="14">
-        <f>Z42-Z46</f>
-        <v/>
-      </c>
-      <c r="AA47" s="14">
-        <f>AA42-AA46</f>
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>前月繰越（月初残高）</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="19">
+        <f>B48</f>
+        <v/>
+      </c>
+      <c r="D47" s="19">
+        <f>C48</f>
+        <v/>
+      </c>
+      <c r="E47" s="19">
+        <f>D48</f>
+        <v/>
+      </c>
+      <c r="F47" s="19">
+        <f>E48</f>
+        <v/>
+      </c>
+      <c r="G47" s="19">
+        <f>F48</f>
+        <v/>
+      </c>
+      <c r="H47" s="19">
+        <f>G48</f>
+        <v/>
+      </c>
+      <c r="I47" s="19">
+        <f>H48</f>
+        <v/>
+      </c>
+      <c r="J47" s="19">
+        <f>I48</f>
+        <v/>
+      </c>
+      <c r="K47" s="19">
+        <f>J48</f>
+        <v/>
+      </c>
+      <c r="L47" s="19">
+        <f>K48</f>
+        <v/>
+      </c>
+      <c r="M47" s="19">
+        <f>L48</f>
+        <v/>
+      </c>
+      <c r="N47" s="19">
+        <f>M48</f>
+        <v/>
+      </c>
+      <c r="O47" s="19">
+        <f>N48</f>
+        <v/>
+      </c>
+      <c r="P47" s="19">
+        <f>O48</f>
+        <v/>
+      </c>
+      <c r="Q47" s="19">
+        <f>P48</f>
+        <v/>
+      </c>
+      <c r="R47" s="19">
+        <f>Q48</f>
+        <v/>
+      </c>
+      <c r="S47" s="19">
+        <f>R48</f>
+        <v/>
+      </c>
+      <c r="T47" s="19">
+        <f>S48</f>
+        <v/>
+      </c>
+      <c r="U47" s="19">
+        <f>T48</f>
+        <v/>
+      </c>
+      <c r="V47" s="19">
+        <f>U48</f>
+        <v/>
+      </c>
+      <c r="W47" s="19">
+        <f>V48</f>
+        <v/>
+      </c>
+      <c r="X47" s="19">
+        <f>W48</f>
+        <v/>
+      </c>
+      <c r="Y47" s="19">
+        <f>X48</f>
+        <v/>
+      </c>
+      <c r="Z47" s="19">
+        <f>Y48</f>
+        <v/>
+      </c>
+      <c r="AA47" s="19">
+        <f>B47</f>
         <v/>
       </c>
     </row>
@@ -3109,107 +3130,107 @@
           <t>翌月繰越（月末残高）</t>
         </is>
       </c>
-      <c r="B48" s="14">
-        <f>B8+B27+B37+B47</f>
-        <v/>
-      </c>
-      <c r="C48" s="14">
-        <f>C8+C27+C37+C47</f>
-        <v/>
-      </c>
-      <c r="D48" s="14">
-        <f>D8+D27+D37+D47</f>
-        <v/>
-      </c>
-      <c r="E48" s="14">
-        <f>E8+E27+E37+E47</f>
-        <v/>
-      </c>
-      <c r="F48" s="14">
-        <f>F8+F27+F37+F47</f>
-        <v/>
-      </c>
-      <c r="G48" s="14">
-        <f>G8+G27+G37+G47</f>
-        <v/>
-      </c>
-      <c r="H48" s="14">
-        <f>H8+H27+H37+H47</f>
-        <v/>
-      </c>
-      <c r="I48" s="14">
-        <f>I8+I27+I37+I47</f>
-        <v/>
-      </c>
-      <c r="J48" s="14">
-        <f>J8+J27+J37+J47</f>
-        <v/>
-      </c>
-      <c r="K48" s="14">
-        <f>K8+K27+K37+K47</f>
-        <v/>
-      </c>
-      <c r="L48" s="14">
-        <f>L8+L27+L37+L47</f>
-        <v/>
-      </c>
-      <c r="M48" s="14">
-        <f>M8+M27+M37+M47</f>
-        <v/>
-      </c>
-      <c r="N48" s="14">
-        <f>N8+N27+N37+N47</f>
-        <v/>
-      </c>
-      <c r="O48" s="14">
-        <f>O8+O27+O37+O47</f>
-        <v/>
-      </c>
-      <c r="P48" s="14">
-        <f>P8+P27+P37+P47</f>
-        <v/>
-      </c>
-      <c r="Q48" s="14">
-        <f>Q8+Q27+Q37+Q47</f>
-        <v/>
-      </c>
-      <c r="R48" s="14">
-        <f>R8+R27+R37+R47</f>
-        <v/>
-      </c>
-      <c r="S48" s="14">
-        <f>S8+S27+S37+S47</f>
-        <v/>
-      </c>
-      <c r="T48" s="14">
-        <f>T8+T27+T37+T47</f>
-        <v/>
-      </c>
-      <c r="U48" s="14">
-        <f>U8+U27+U37+U47</f>
-        <v/>
-      </c>
-      <c r="V48" s="14">
-        <f>V8+V27+V37+V47</f>
-        <v/>
-      </c>
-      <c r="W48" s="14">
-        <f>W8+W27+W37+W47</f>
-        <v/>
-      </c>
-      <c r="X48" s="14">
-        <f>X8+X27+X37+X47</f>
-        <v/>
-      </c>
-      <c r="Y48" s="14">
-        <f>Y8+Y27+Y37+Y47</f>
-        <v/>
-      </c>
-      <c r="Z48" s="14">
-        <f>Z8+Z27+Z37+Z47</f>
-        <v/>
-      </c>
-      <c r="AA48" s="14">
+      <c r="B48" s="19">
+        <f>B47+B26+B36+B46</f>
+        <v/>
+      </c>
+      <c r="C48" s="19">
+        <f>C47+C26+C36+C46</f>
+        <v/>
+      </c>
+      <c r="D48" s="19">
+        <f>D47+D26+D36+D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="19">
+        <f>E47+E26+E36+E46</f>
+        <v/>
+      </c>
+      <c r="F48" s="19">
+        <f>F47+F26+F36+F46</f>
+        <v/>
+      </c>
+      <c r="G48" s="19">
+        <f>G47+G26+G36+G46</f>
+        <v/>
+      </c>
+      <c r="H48" s="19">
+        <f>H47+H26+H36+H46</f>
+        <v/>
+      </c>
+      <c r="I48" s="19">
+        <f>I47+I26+I36+I46</f>
+        <v/>
+      </c>
+      <c r="J48" s="19">
+        <f>J47+J26+J36+J46</f>
+        <v/>
+      </c>
+      <c r="K48" s="19">
+        <f>K47+K26+K36+K46</f>
+        <v/>
+      </c>
+      <c r="L48" s="19">
+        <f>L47+L26+L36+L46</f>
+        <v/>
+      </c>
+      <c r="M48" s="19">
+        <f>M47+M26+M36+M46</f>
+        <v/>
+      </c>
+      <c r="N48" s="19">
+        <f>N47+N26+N36+N46</f>
+        <v/>
+      </c>
+      <c r="O48" s="19">
+        <f>O47+O26+O36+O46</f>
+        <v/>
+      </c>
+      <c r="P48" s="19">
+        <f>P47+P26+P36+P46</f>
+        <v/>
+      </c>
+      <c r="Q48" s="19">
+        <f>Q47+Q26+Q36+Q46</f>
+        <v/>
+      </c>
+      <c r="R48" s="19">
+        <f>R47+R26+R36+R46</f>
+        <v/>
+      </c>
+      <c r="S48" s="19">
+        <f>S47+S26+S36+S46</f>
+        <v/>
+      </c>
+      <c r="T48" s="19">
+        <f>T47+T26+T36+T46</f>
+        <v/>
+      </c>
+      <c r="U48" s="19">
+        <f>U47+U26+U36+U46</f>
+        <v/>
+      </c>
+      <c r="V48" s="19">
+        <f>V47+V26+V36+V46</f>
+        <v/>
+      </c>
+      <c r="W48" s="19">
+        <f>W47+W26+W36+W46</f>
+        <v/>
+      </c>
+      <c r="X48" s="19">
+        <f>X47+X26+X36+X46</f>
+        <v/>
+      </c>
+      <c r="Y48" s="19">
+        <f>Y47+Y26+Y36+Y46</f>
+        <v/>
+      </c>
+      <c r="Z48" s="19">
+        <f>Z47+Z26+Z36+Z46</f>
+        <v/>
+      </c>
+      <c r="AA48" s="19">
         <f>Z48</f>
         <v/>
       </c>
@@ -3322,7 +3343,1781 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>滞納管理（保険料・税）※資金収支の計算には含めない</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="22" t="n"/>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="22" t="n"/>
+      <c r="J51" s="22" t="n"/>
+      <c r="K51" s="22" t="n"/>
+      <c r="L51" s="22" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="22" t="n"/>
+      <c r="O51" s="22" t="n"/>
+      <c r="P51" s="22" t="n"/>
+      <c r="Q51" s="22" t="n"/>
+      <c r="R51" s="22" t="n"/>
+      <c r="S51" s="22" t="n"/>
+      <c r="T51" s="22" t="n"/>
+      <c r="U51" s="22" t="n"/>
+      <c r="V51" s="22" t="n"/>
+      <c r="W51" s="22" t="n"/>
+      <c r="X51" s="22" t="n"/>
+      <c r="Y51" s="22" t="n"/>
+      <c r="Z51" s="22" t="n"/>
+      <c r="AA51" s="22" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>社会保険料（健康保険・厚生年金）</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n"/>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="23" t="n"/>
+      <c r="E52" s="23" t="n"/>
+      <c r="F52" s="23" t="n"/>
+      <c r="G52" s="23" t="n"/>
+      <c r="H52" s="23" t="n"/>
+      <c r="I52" s="23" t="n"/>
+      <c r="J52" s="23" t="n"/>
+      <c r="K52" s="23" t="n"/>
+      <c r="L52" s="23" t="n"/>
+      <c r="M52" s="23" t="n"/>
+      <c r="N52" s="23" t="n"/>
+      <c r="O52" s="23" t="n"/>
+      <c r="P52" s="23" t="n"/>
+      <c r="Q52" s="23" t="n"/>
+      <c r="R52" s="23" t="n"/>
+      <c r="S52" s="23" t="n"/>
+      <c r="T52" s="23" t="n"/>
+      <c r="U52" s="23" t="n"/>
+      <c r="V52" s="23" t="n"/>
+      <c r="W52" s="23" t="n"/>
+      <c r="X52" s="23" t="n"/>
+      <c r="Y52" s="23" t="n"/>
+      <c r="Z52" s="23" t="n"/>
+      <c r="AA52" s="23" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本来の納付額</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
+      <c r="I53" s="9" t="n"/>
+      <c r="J53" s="9" t="n"/>
+      <c r="K53" s="9" t="n"/>
+      <c r="L53" s="9" t="n"/>
+      <c r="M53" s="9" t="n"/>
+      <c r="N53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
+      <c r="P53" s="9" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="9" t="n"/>
+      <c r="S53" s="9" t="n"/>
+      <c r="T53" s="9" t="n"/>
+      <c r="U53" s="9" t="n"/>
+      <c r="V53" s="9" t="n"/>
+      <c r="W53" s="9" t="n"/>
+      <c r="X53" s="9" t="n"/>
+      <c r="Y53" s="9" t="n"/>
+      <c r="Z53" s="9" t="n"/>
+      <c r="AA53" s="15">
+        <f>SUM(B53:Z53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実際の納付額</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+      <c r="L54" s="9" t="n"/>
+      <c r="M54" s="9" t="n"/>
+      <c r="N54" s="9" t="n"/>
+      <c r="O54" s="9" t="n"/>
+      <c r="P54" s="9" t="n"/>
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="9" t="n"/>
+      <c r="S54" s="9" t="n"/>
+      <c r="T54" s="9" t="n"/>
+      <c r="U54" s="9" t="n"/>
+      <c r="V54" s="9" t="n"/>
+      <c r="W54" s="9" t="n"/>
+      <c r="X54" s="9" t="n"/>
+      <c r="Y54" s="9" t="n"/>
+      <c r="Z54" s="9" t="n"/>
+      <c r="AA54" s="15">
+        <f>SUM(B54:Z54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  滞納残高（累計）</t>
+        </is>
+      </c>
+      <c r="B55" s="17">
+        <f>B53-B54</f>
+        <v/>
+      </c>
+      <c r="C55" s="17">
+        <f>B55+C53-C54</f>
+        <v/>
+      </c>
+      <c r="D55" s="17">
+        <f>C55+D53-D54</f>
+        <v/>
+      </c>
+      <c r="E55" s="17">
+        <f>D55+E53-E54</f>
+        <v/>
+      </c>
+      <c r="F55" s="17">
+        <f>E55+F53-F54</f>
+        <v/>
+      </c>
+      <c r="G55" s="17">
+        <f>F55+G53-G54</f>
+        <v/>
+      </c>
+      <c r="H55" s="17">
+        <f>G55+H53-H54</f>
+        <v/>
+      </c>
+      <c r="I55" s="17">
+        <f>H55+I53-I54</f>
+        <v/>
+      </c>
+      <c r="J55" s="17">
+        <f>I55+J53-J54</f>
+        <v/>
+      </c>
+      <c r="K55" s="17">
+        <f>J55+K53-K54</f>
+        <v/>
+      </c>
+      <c r="L55" s="17">
+        <f>K55+L53-L54</f>
+        <v/>
+      </c>
+      <c r="M55" s="17">
+        <f>L55+M53-M54</f>
+        <v/>
+      </c>
+      <c r="N55" s="17">
+        <f>M55+N53-N54</f>
+        <v/>
+      </c>
+      <c r="O55" s="17">
+        <f>N55+O53-O54</f>
+        <v/>
+      </c>
+      <c r="P55" s="17">
+        <f>O55+P53-P54</f>
+        <v/>
+      </c>
+      <c r="Q55" s="17">
+        <f>P55+Q53-Q54</f>
+        <v/>
+      </c>
+      <c r="R55" s="17">
+        <f>Q55+R53-R54</f>
+        <v/>
+      </c>
+      <c r="S55" s="17">
+        <f>R55+S53-S54</f>
+        <v/>
+      </c>
+      <c r="T55" s="17">
+        <f>S55+T53-T54</f>
+        <v/>
+      </c>
+      <c r="U55" s="17">
+        <f>T55+U53-U54</f>
+        <v/>
+      </c>
+      <c r="V55" s="17">
+        <f>U55+V53-V54</f>
+        <v/>
+      </c>
+      <c r="W55" s="17">
+        <f>V55+W53-W54</f>
+        <v/>
+      </c>
+      <c r="X55" s="17">
+        <f>W55+X53-X54</f>
+        <v/>
+      </c>
+      <c r="Y55" s="17">
+        <f>X55+Y53-Y54</f>
+        <v/>
+      </c>
+      <c r="Z55" s="17">
+        <f>Y55+Z53-Z54</f>
+        <v/>
+      </c>
+      <c r="AA55" s="17">
+        <f>Z55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>労働保険料</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="n"/>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="23" t="n"/>
+      <c r="F56" s="23" t="n"/>
+      <c r="G56" s="23" t="n"/>
+      <c r="H56" s="23" t="n"/>
+      <c r="I56" s="23" t="n"/>
+      <c r="J56" s="23" t="n"/>
+      <c r="K56" s="23" t="n"/>
+      <c r="L56" s="23" t="n"/>
+      <c r="M56" s="23" t="n"/>
+      <c r="N56" s="23" t="n"/>
+      <c r="O56" s="23" t="n"/>
+      <c r="P56" s="23" t="n"/>
+      <c r="Q56" s="23" t="n"/>
+      <c r="R56" s="23" t="n"/>
+      <c r="S56" s="23" t="n"/>
+      <c r="T56" s="23" t="n"/>
+      <c r="U56" s="23" t="n"/>
+      <c r="V56" s="23" t="n"/>
+      <c r="W56" s="23" t="n"/>
+      <c r="X56" s="23" t="n"/>
+      <c r="Y56" s="23" t="n"/>
+      <c r="Z56" s="23" t="n"/>
+      <c r="AA56" s="23" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本来の納付額</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="9" t="n"/>
+      <c r="O57" s="9" t="n"/>
+      <c r="P57" s="9" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="9" t="n"/>
+      <c r="S57" s="9" t="n"/>
+      <c r="T57" s="9" t="n"/>
+      <c r="U57" s="9" t="n"/>
+      <c r="V57" s="9" t="n"/>
+      <c r="W57" s="9" t="n"/>
+      <c r="X57" s="9" t="n"/>
+      <c r="Y57" s="9" t="n"/>
+      <c r="Z57" s="9" t="n"/>
+      <c r="AA57" s="15">
+        <f>SUM(B57:Z57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実際の納付額</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="n"/>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
+      <c r="L58" s="9" t="n"/>
+      <c r="M58" s="9" t="n"/>
+      <c r="N58" s="9" t="n"/>
+      <c r="O58" s="9" t="n"/>
+      <c r="P58" s="9" t="n"/>
+      <c r="Q58" s="9" t="n"/>
+      <c r="R58" s="9" t="n"/>
+      <c r="S58" s="9" t="n"/>
+      <c r="T58" s="9" t="n"/>
+      <c r="U58" s="9" t="n"/>
+      <c r="V58" s="9" t="n"/>
+      <c r="W58" s="9" t="n"/>
+      <c r="X58" s="9" t="n"/>
+      <c r="Y58" s="9" t="n"/>
+      <c r="Z58" s="9" t="n"/>
+      <c r="AA58" s="15">
+        <f>SUM(B58:Z58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  滞納残高（累計）</t>
+        </is>
+      </c>
+      <c r="B59" s="17">
+        <f>B57-B58</f>
+        <v/>
+      </c>
+      <c r="C59" s="17">
+        <f>B59+C57-C58</f>
+        <v/>
+      </c>
+      <c r="D59" s="17">
+        <f>C59+D57-D58</f>
+        <v/>
+      </c>
+      <c r="E59" s="17">
+        <f>D59+E57-E58</f>
+        <v/>
+      </c>
+      <c r="F59" s="17">
+        <f>E59+F57-F58</f>
+        <v/>
+      </c>
+      <c r="G59" s="17">
+        <f>F59+G57-G58</f>
+        <v/>
+      </c>
+      <c r="H59" s="17">
+        <f>G59+H57-H58</f>
+        <v/>
+      </c>
+      <c r="I59" s="17">
+        <f>H59+I57-I58</f>
+        <v/>
+      </c>
+      <c r="J59" s="17">
+        <f>I59+J57-J58</f>
+        <v/>
+      </c>
+      <c r="K59" s="17">
+        <f>J59+K57-K58</f>
+        <v/>
+      </c>
+      <c r="L59" s="17">
+        <f>K59+L57-L58</f>
+        <v/>
+      </c>
+      <c r="M59" s="17">
+        <f>L59+M57-M58</f>
+        <v/>
+      </c>
+      <c r="N59" s="17">
+        <f>M59+N57-N58</f>
+        <v/>
+      </c>
+      <c r="O59" s="17">
+        <f>N59+O57-O58</f>
+        <v/>
+      </c>
+      <c r="P59" s="17">
+        <f>O59+P57-P58</f>
+        <v/>
+      </c>
+      <c r="Q59" s="17">
+        <f>P59+Q57-Q58</f>
+        <v/>
+      </c>
+      <c r="R59" s="17">
+        <f>Q59+R57-R58</f>
+        <v/>
+      </c>
+      <c r="S59" s="17">
+        <f>R59+S57-S58</f>
+        <v/>
+      </c>
+      <c r="T59" s="17">
+        <f>S59+T57-T58</f>
+        <v/>
+      </c>
+      <c r="U59" s="17">
+        <f>T59+U57-U58</f>
+        <v/>
+      </c>
+      <c r="V59" s="17">
+        <f>U59+V57-V58</f>
+        <v/>
+      </c>
+      <c r="W59" s="17">
+        <f>V59+W57-W58</f>
+        <v/>
+      </c>
+      <c r="X59" s="17">
+        <f>W59+X57-X58</f>
+        <v/>
+      </c>
+      <c r="Y59" s="17">
+        <f>X59+Y57-Y58</f>
+        <v/>
+      </c>
+      <c r="Z59" s="17">
+        <f>Y59+Z57-Z58</f>
+        <v/>
+      </c>
+      <c r="AA59" s="17">
+        <f>Z59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>源泉所得税</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="n"/>
+      <c r="C60" s="23" t="n"/>
+      <c r="D60" s="23" t="n"/>
+      <c r="E60" s="23" t="n"/>
+      <c r="F60" s="23" t="n"/>
+      <c r="G60" s="23" t="n"/>
+      <c r="H60" s="23" t="n"/>
+      <c r="I60" s="23" t="n"/>
+      <c r="J60" s="23" t="n"/>
+      <c r="K60" s="23" t="n"/>
+      <c r="L60" s="23" t="n"/>
+      <c r="M60" s="23" t="n"/>
+      <c r="N60" s="23" t="n"/>
+      <c r="O60" s="23" t="n"/>
+      <c r="P60" s="23" t="n"/>
+      <c r="Q60" s="23" t="n"/>
+      <c r="R60" s="23" t="n"/>
+      <c r="S60" s="23" t="n"/>
+      <c r="T60" s="23" t="n"/>
+      <c r="U60" s="23" t="n"/>
+      <c r="V60" s="23" t="n"/>
+      <c r="W60" s="23" t="n"/>
+      <c r="X60" s="23" t="n"/>
+      <c r="Y60" s="23" t="n"/>
+      <c r="Z60" s="23" t="n"/>
+      <c r="AA60" s="23" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本来の納付額</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+      <c r="L61" s="9" t="n"/>
+      <c r="M61" s="9" t="n"/>
+      <c r="N61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
+      <c r="P61" s="9" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="9" t="n"/>
+      <c r="S61" s="9" t="n"/>
+      <c r="T61" s="9" t="n"/>
+      <c r="U61" s="9" t="n"/>
+      <c r="V61" s="9" t="n"/>
+      <c r="W61" s="9" t="n"/>
+      <c r="X61" s="9" t="n"/>
+      <c r="Y61" s="9" t="n"/>
+      <c r="Z61" s="9" t="n"/>
+      <c r="AA61" s="15">
+        <f>SUM(B61:Z61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実際の納付額</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="9" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="9" t="n"/>
+      <c r="H62" s="9" t="n"/>
+      <c r="I62" s="9" t="n"/>
+      <c r="J62" s="9" t="n"/>
+      <c r="K62" s="9" t="n"/>
+      <c r="L62" s="9" t="n"/>
+      <c r="M62" s="9" t="n"/>
+      <c r="N62" s="9" t="n"/>
+      <c r="O62" s="9" t="n"/>
+      <c r="P62" s="9" t="n"/>
+      <c r="Q62" s="9" t="n"/>
+      <c r="R62" s="9" t="n"/>
+      <c r="S62" s="9" t="n"/>
+      <c r="T62" s="9" t="n"/>
+      <c r="U62" s="9" t="n"/>
+      <c r="V62" s="9" t="n"/>
+      <c r="W62" s="9" t="n"/>
+      <c r="X62" s="9" t="n"/>
+      <c r="Y62" s="9" t="n"/>
+      <c r="Z62" s="9" t="n"/>
+      <c r="AA62" s="15">
+        <f>SUM(B62:Z62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  滞納残高（累計）</t>
+        </is>
+      </c>
+      <c r="B63" s="17">
+        <f>B61-B62</f>
+        <v/>
+      </c>
+      <c r="C63" s="17">
+        <f>B63+C61-C62</f>
+        <v/>
+      </c>
+      <c r="D63" s="17">
+        <f>C63+D61-D62</f>
+        <v/>
+      </c>
+      <c r="E63" s="17">
+        <f>D63+E61-E62</f>
+        <v/>
+      </c>
+      <c r="F63" s="17">
+        <f>E63+F61-F62</f>
+        <v/>
+      </c>
+      <c r="G63" s="17">
+        <f>F63+G61-G62</f>
+        <v/>
+      </c>
+      <c r="H63" s="17">
+        <f>G63+H61-H62</f>
+        <v/>
+      </c>
+      <c r="I63" s="17">
+        <f>H63+I61-I62</f>
+        <v/>
+      </c>
+      <c r="J63" s="17">
+        <f>I63+J61-J62</f>
+        <v/>
+      </c>
+      <c r="K63" s="17">
+        <f>J63+K61-K62</f>
+        <v/>
+      </c>
+      <c r="L63" s="17">
+        <f>K63+L61-L62</f>
+        <v/>
+      </c>
+      <c r="M63" s="17">
+        <f>L63+M61-M62</f>
+        <v/>
+      </c>
+      <c r="N63" s="17">
+        <f>M63+N61-N62</f>
+        <v/>
+      </c>
+      <c r="O63" s="17">
+        <f>N63+O61-O62</f>
+        <v/>
+      </c>
+      <c r="P63" s="17">
+        <f>O63+P61-P62</f>
+        <v/>
+      </c>
+      <c r="Q63" s="17">
+        <f>P63+Q61-Q62</f>
+        <v/>
+      </c>
+      <c r="R63" s="17">
+        <f>Q63+R61-R62</f>
+        <v/>
+      </c>
+      <c r="S63" s="17">
+        <f>R63+S61-S62</f>
+        <v/>
+      </c>
+      <c r="T63" s="17">
+        <f>S63+T61-T62</f>
+        <v/>
+      </c>
+      <c r="U63" s="17">
+        <f>T63+U61-U62</f>
+        <v/>
+      </c>
+      <c r="V63" s="17">
+        <f>U63+V61-V62</f>
+        <v/>
+      </c>
+      <c r="W63" s="17">
+        <f>V63+W61-W62</f>
+        <v/>
+      </c>
+      <c r="X63" s="17">
+        <f>W63+X61-X62</f>
+        <v/>
+      </c>
+      <c r="Y63" s="17">
+        <f>X63+Y61-Y62</f>
+        <v/>
+      </c>
+      <c r="Z63" s="17">
+        <f>Y63+Z61-Z62</f>
+        <v/>
+      </c>
+      <c r="AA63" s="17">
+        <f>Z63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>住民税（特別徴収）</t>
+        </is>
+      </c>
+      <c r="B64" s="23" t="n"/>
+      <c r="C64" s="23" t="n"/>
+      <c r="D64" s="23" t="n"/>
+      <c r="E64" s="23" t="n"/>
+      <c r="F64" s="23" t="n"/>
+      <c r="G64" s="23" t="n"/>
+      <c r="H64" s="23" t="n"/>
+      <c r="I64" s="23" t="n"/>
+      <c r="J64" s="23" t="n"/>
+      <c r="K64" s="23" t="n"/>
+      <c r="L64" s="23" t="n"/>
+      <c r="M64" s="23" t="n"/>
+      <c r="N64" s="23" t="n"/>
+      <c r="O64" s="23" t="n"/>
+      <c r="P64" s="23" t="n"/>
+      <c r="Q64" s="23" t="n"/>
+      <c r="R64" s="23" t="n"/>
+      <c r="S64" s="23" t="n"/>
+      <c r="T64" s="23" t="n"/>
+      <c r="U64" s="23" t="n"/>
+      <c r="V64" s="23" t="n"/>
+      <c r="W64" s="23" t="n"/>
+      <c r="X64" s="23" t="n"/>
+      <c r="Y64" s="23" t="n"/>
+      <c r="Z64" s="23" t="n"/>
+      <c r="AA64" s="23" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本来の納付額</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
+      <c r="L65" s="9" t="n"/>
+      <c r="M65" s="9" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="9" t="n"/>
+      <c r="P65" s="9" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="9" t="n"/>
+      <c r="S65" s="9" t="n"/>
+      <c r="T65" s="9" t="n"/>
+      <c r="U65" s="9" t="n"/>
+      <c r="V65" s="9" t="n"/>
+      <c r="W65" s="9" t="n"/>
+      <c r="X65" s="9" t="n"/>
+      <c r="Y65" s="9" t="n"/>
+      <c r="Z65" s="9" t="n"/>
+      <c r="AA65" s="15">
+        <f>SUM(B65:Z65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実際の納付額</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="9" t="n"/>
+      <c r="L66" s="9" t="n"/>
+      <c r="M66" s="9" t="n"/>
+      <c r="N66" s="9" t="n"/>
+      <c r="O66" s="9" t="n"/>
+      <c r="P66" s="9" t="n"/>
+      <c r="Q66" s="9" t="n"/>
+      <c r="R66" s="9" t="n"/>
+      <c r="S66" s="9" t="n"/>
+      <c r="T66" s="9" t="n"/>
+      <c r="U66" s="9" t="n"/>
+      <c r="V66" s="9" t="n"/>
+      <c r="W66" s="9" t="n"/>
+      <c r="X66" s="9" t="n"/>
+      <c r="Y66" s="9" t="n"/>
+      <c r="Z66" s="9" t="n"/>
+      <c r="AA66" s="15">
+        <f>SUM(B66:Z66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  滞納残高（累計）</t>
+        </is>
+      </c>
+      <c r="B67" s="17">
+        <f>B65-B66</f>
+        <v/>
+      </c>
+      <c r="C67" s="17">
+        <f>B67+C65-C66</f>
+        <v/>
+      </c>
+      <c r="D67" s="17">
+        <f>C67+D65-D66</f>
+        <v/>
+      </c>
+      <c r="E67" s="17">
+        <f>D67+E65-E66</f>
+        <v/>
+      </c>
+      <c r="F67" s="17">
+        <f>E67+F65-F66</f>
+        <v/>
+      </c>
+      <c r="G67" s="17">
+        <f>F67+G65-G66</f>
+        <v/>
+      </c>
+      <c r="H67" s="17">
+        <f>G67+H65-H66</f>
+        <v/>
+      </c>
+      <c r="I67" s="17">
+        <f>H67+I65-I66</f>
+        <v/>
+      </c>
+      <c r="J67" s="17">
+        <f>I67+J65-J66</f>
+        <v/>
+      </c>
+      <c r="K67" s="17">
+        <f>J67+K65-K66</f>
+        <v/>
+      </c>
+      <c r="L67" s="17">
+        <f>K67+L65-L66</f>
+        <v/>
+      </c>
+      <c r="M67" s="17">
+        <f>L67+M65-M66</f>
+        <v/>
+      </c>
+      <c r="N67" s="17">
+        <f>M67+N65-N66</f>
+        <v/>
+      </c>
+      <c r="O67" s="17">
+        <f>N67+O65-O66</f>
+        <v/>
+      </c>
+      <c r="P67" s="17">
+        <f>O67+P65-P66</f>
+        <v/>
+      </c>
+      <c r="Q67" s="17">
+        <f>P67+Q65-Q66</f>
+        <v/>
+      </c>
+      <c r="R67" s="17">
+        <f>Q67+R65-R66</f>
+        <v/>
+      </c>
+      <c r="S67" s="17">
+        <f>R67+S65-S66</f>
+        <v/>
+      </c>
+      <c r="T67" s="17">
+        <f>S67+T65-T66</f>
+        <v/>
+      </c>
+      <c r="U67" s="17">
+        <f>T67+U65-U66</f>
+        <v/>
+      </c>
+      <c r="V67" s="17">
+        <f>U67+V65-V66</f>
+        <v/>
+      </c>
+      <c r="W67" s="17">
+        <f>V67+W65-W66</f>
+        <v/>
+      </c>
+      <c r="X67" s="17">
+        <f>W67+X65-X66</f>
+        <v/>
+      </c>
+      <c r="Y67" s="17">
+        <f>X67+Y65-Y66</f>
+        <v/>
+      </c>
+      <c r="Z67" s="17">
+        <f>Y67+Z65-Z66</f>
+        <v/>
+      </c>
+      <c r="AA67" s="17">
+        <f>Z67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>消費税</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="n"/>
+      <c r="C68" s="23" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="23" t="n"/>
+      <c r="F68" s="23" t="n"/>
+      <c r="G68" s="23" t="n"/>
+      <c r="H68" s="23" t="n"/>
+      <c r="I68" s="23" t="n"/>
+      <c r="J68" s="23" t="n"/>
+      <c r="K68" s="23" t="n"/>
+      <c r="L68" s="23" t="n"/>
+      <c r="M68" s="23" t="n"/>
+      <c r="N68" s="23" t="n"/>
+      <c r="O68" s="23" t="n"/>
+      <c r="P68" s="23" t="n"/>
+      <c r="Q68" s="23" t="n"/>
+      <c r="R68" s="23" t="n"/>
+      <c r="S68" s="23" t="n"/>
+      <c r="T68" s="23" t="n"/>
+      <c r="U68" s="23" t="n"/>
+      <c r="V68" s="23" t="n"/>
+      <c r="W68" s="23" t="n"/>
+      <c r="X68" s="23" t="n"/>
+      <c r="Y68" s="23" t="n"/>
+      <c r="Z68" s="23" t="n"/>
+      <c r="AA68" s="23" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本来の納付額</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="9" t="n"/>
+      <c r="H69" s="9" t="n"/>
+      <c r="I69" s="9" t="n"/>
+      <c r="J69" s="9" t="n"/>
+      <c r="K69" s="9" t="n"/>
+      <c r="L69" s="9" t="n"/>
+      <c r="M69" s="9" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="9" t="n"/>
+      <c r="P69" s="9" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="9" t="n"/>
+      <c r="S69" s="9" t="n"/>
+      <c r="T69" s="9" t="n"/>
+      <c r="U69" s="9" t="n"/>
+      <c r="V69" s="9" t="n"/>
+      <c r="W69" s="9" t="n"/>
+      <c r="X69" s="9" t="n"/>
+      <c r="Y69" s="9" t="n"/>
+      <c r="Z69" s="9" t="n"/>
+      <c r="AA69" s="15">
+        <f>SUM(B69:Z69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実際の納付額</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
+      <c r="L70" s="9" t="n"/>
+      <c r="M70" s="9" t="n"/>
+      <c r="N70" s="9" t="n"/>
+      <c r="O70" s="9" t="n"/>
+      <c r="P70" s="9" t="n"/>
+      <c r="Q70" s="9" t="n"/>
+      <c r="R70" s="9" t="n"/>
+      <c r="S70" s="9" t="n"/>
+      <c r="T70" s="9" t="n"/>
+      <c r="U70" s="9" t="n"/>
+      <c r="V70" s="9" t="n"/>
+      <c r="W70" s="9" t="n"/>
+      <c r="X70" s="9" t="n"/>
+      <c r="Y70" s="9" t="n"/>
+      <c r="Z70" s="9" t="n"/>
+      <c r="AA70" s="15">
+        <f>SUM(B70:Z70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  滞納残高（累計）</t>
+        </is>
+      </c>
+      <c r="B71" s="17">
+        <f>B69-B70</f>
+        <v/>
+      </c>
+      <c r="C71" s="17">
+        <f>B71+C69-C70</f>
+        <v/>
+      </c>
+      <c r="D71" s="17">
+        <f>C71+D69-D70</f>
+        <v/>
+      </c>
+      <c r="E71" s="17">
+        <f>D71+E69-E70</f>
+        <v/>
+      </c>
+      <c r="F71" s="17">
+        <f>E71+F69-F70</f>
+        <v/>
+      </c>
+      <c r="G71" s="17">
+        <f>F71+G69-G70</f>
+        <v/>
+      </c>
+      <c r="H71" s="17">
+        <f>G71+H69-H70</f>
+        <v/>
+      </c>
+      <c r="I71" s="17">
+        <f>H71+I69-I70</f>
+        <v/>
+      </c>
+      <c r="J71" s="17">
+        <f>I71+J69-J70</f>
+        <v/>
+      </c>
+      <c r="K71" s="17">
+        <f>J71+K69-K70</f>
+        <v/>
+      </c>
+      <c r="L71" s="17">
+        <f>K71+L69-L70</f>
+        <v/>
+      </c>
+      <c r="M71" s="17">
+        <f>L71+M69-M70</f>
+        <v/>
+      </c>
+      <c r="N71" s="17">
+        <f>M71+N69-N70</f>
+        <v/>
+      </c>
+      <c r="O71" s="17">
+        <f>N71+O69-O70</f>
+        <v/>
+      </c>
+      <c r="P71" s="17">
+        <f>O71+P69-P70</f>
+        <v/>
+      </c>
+      <c r="Q71" s="17">
+        <f>P71+Q69-Q70</f>
+        <v/>
+      </c>
+      <c r="R71" s="17">
+        <f>Q71+R69-R70</f>
+        <v/>
+      </c>
+      <c r="S71" s="17">
+        <f>R71+S69-S70</f>
+        <v/>
+      </c>
+      <c r="T71" s="17">
+        <f>S71+T69-T70</f>
+        <v/>
+      </c>
+      <c r="U71" s="17">
+        <f>T71+U69-U70</f>
+        <v/>
+      </c>
+      <c r="V71" s="17">
+        <f>U71+V69-V70</f>
+        <v/>
+      </c>
+      <c r="W71" s="17">
+        <f>V71+W69-W70</f>
+        <v/>
+      </c>
+      <c r="X71" s="17">
+        <f>W71+X69-X70</f>
+        <v/>
+      </c>
+      <c r="Y71" s="17">
+        <f>X71+Y69-Y70</f>
+        <v/>
+      </c>
+      <c r="Z71" s="17">
+        <f>Y71+Z69-Z70</f>
+        <v/>
+      </c>
+      <c r="AA71" s="17">
+        <f>Z71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>法人税・地方税等</t>
+        </is>
+      </c>
+      <c r="B72" s="23" t="n"/>
+      <c r="C72" s="23" t="n"/>
+      <c r="D72" s="23" t="n"/>
+      <c r="E72" s="23" t="n"/>
+      <c r="F72" s="23" t="n"/>
+      <c r="G72" s="23" t="n"/>
+      <c r="H72" s="23" t="n"/>
+      <c r="I72" s="23" t="n"/>
+      <c r="J72" s="23" t="n"/>
+      <c r="K72" s="23" t="n"/>
+      <c r="L72" s="23" t="n"/>
+      <c r="M72" s="23" t="n"/>
+      <c r="N72" s="23" t="n"/>
+      <c r="O72" s="23" t="n"/>
+      <c r="P72" s="23" t="n"/>
+      <c r="Q72" s="23" t="n"/>
+      <c r="R72" s="23" t="n"/>
+      <c r="S72" s="23" t="n"/>
+      <c r="T72" s="23" t="n"/>
+      <c r="U72" s="23" t="n"/>
+      <c r="V72" s="23" t="n"/>
+      <c r="W72" s="23" t="n"/>
+      <c r="X72" s="23" t="n"/>
+      <c r="Y72" s="23" t="n"/>
+      <c r="Z72" s="23" t="n"/>
+      <c r="AA72" s="23" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本来の納付額</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="9" t="n"/>
+      <c r="H73" s="9" t="n"/>
+      <c r="I73" s="9" t="n"/>
+      <c r="J73" s="9" t="n"/>
+      <c r="K73" s="9" t="n"/>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="9" t="n"/>
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="9" t="n"/>
+      <c r="P73" s="9" t="n"/>
+      <c r="Q73" s="9" t="n"/>
+      <c r="R73" s="9" t="n"/>
+      <c r="S73" s="9" t="n"/>
+      <c r="T73" s="9" t="n"/>
+      <c r="U73" s="9" t="n"/>
+      <c r="V73" s="9" t="n"/>
+      <c r="W73" s="9" t="n"/>
+      <c r="X73" s="9" t="n"/>
+      <c r="Y73" s="9" t="n"/>
+      <c r="Z73" s="9" t="n"/>
+      <c r="AA73" s="15">
+        <f>SUM(B73:Z73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実際の納付額</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="n"/>
+      <c r="H74" s="9" t="n"/>
+      <c r="I74" s="9" t="n"/>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
+      <c r="L74" s="9" t="n"/>
+      <c r="M74" s="9" t="n"/>
+      <c r="N74" s="9" t="n"/>
+      <c r="O74" s="9" t="n"/>
+      <c r="P74" s="9" t="n"/>
+      <c r="Q74" s="9" t="n"/>
+      <c r="R74" s="9" t="n"/>
+      <c r="S74" s="9" t="n"/>
+      <c r="T74" s="9" t="n"/>
+      <c r="U74" s="9" t="n"/>
+      <c r="V74" s="9" t="n"/>
+      <c r="W74" s="9" t="n"/>
+      <c r="X74" s="9" t="n"/>
+      <c r="Y74" s="9" t="n"/>
+      <c r="Z74" s="9" t="n"/>
+      <c r="AA74" s="15">
+        <f>SUM(B74:Z74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  滞納残高（累計）</t>
+        </is>
+      </c>
+      <c r="B75" s="17">
+        <f>B73-B74</f>
+        <v/>
+      </c>
+      <c r="C75" s="17">
+        <f>B75+C73-C74</f>
+        <v/>
+      </c>
+      <c r="D75" s="17">
+        <f>C75+D73-D74</f>
+        <v/>
+      </c>
+      <c r="E75" s="17">
+        <f>D75+E73-E74</f>
+        <v/>
+      </c>
+      <c r="F75" s="17">
+        <f>E75+F73-F74</f>
+        <v/>
+      </c>
+      <c r="G75" s="17">
+        <f>F75+G73-G74</f>
+        <v/>
+      </c>
+      <c r="H75" s="17">
+        <f>G75+H73-H74</f>
+        <v/>
+      </c>
+      <c r="I75" s="17">
+        <f>H75+I73-I74</f>
+        <v/>
+      </c>
+      <c r="J75" s="17">
+        <f>I75+J73-J74</f>
+        <v/>
+      </c>
+      <c r="K75" s="17">
+        <f>J75+K73-K74</f>
+        <v/>
+      </c>
+      <c r="L75" s="17">
+        <f>K75+L73-L74</f>
+        <v/>
+      </c>
+      <c r="M75" s="17">
+        <f>L75+M73-M74</f>
+        <v/>
+      </c>
+      <c r="N75" s="17">
+        <f>M75+N73-N74</f>
+        <v/>
+      </c>
+      <c r="O75" s="17">
+        <f>N75+O73-O74</f>
+        <v/>
+      </c>
+      <c r="P75" s="17">
+        <f>O75+P73-P74</f>
+        <v/>
+      </c>
+      <c r="Q75" s="17">
+        <f>P75+Q73-Q74</f>
+        <v/>
+      </c>
+      <c r="R75" s="17">
+        <f>Q75+R73-R74</f>
+        <v/>
+      </c>
+      <c r="S75" s="17">
+        <f>R75+S73-S74</f>
+        <v/>
+      </c>
+      <c r="T75" s="17">
+        <f>S75+T73-T74</f>
+        <v/>
+      </c>
+      <c r="U75" s="17">
+        <f>T75+U73-U74</f>
+        <v/>
+      </c>
+      <c r="V75" s="17">
+        <f>U75+V73-V74</f>
+        <v/>
+      </c>
+      <c r="W75" s="17">
+        <f>V75+W73-W74</f>
+        <v/>
+      </c>
+      <c r="X75" s="17">
+        <f>W75+X73-X74</f>
+        <v/>
+      </c>
+      <c r="Y75" s="17">
+        <f>X75+Y73-Y74</f>
+        <v/>
+      </c>
+      <c r="Z75" s="17">
+        <f>Y75+Z73-Z74</f>
+        <v/>
+      </c>
+      <c r="AA75" s="17">
+        <f>Z75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>その他（延滞金等）</t>
+        </is>
+      </c>
+      <c r="B76" s="23" t="n"/>
+      <c r="C76" s="23" t="n"/>
+      <c r="D76" s="23" t="n"/>
+      <c r="E76" s="23" t="n"/>
+      <c r="F76" s="23" t="n"/>
+      <c r="G76" s="23" t="n"/>
+      <c r="H76" s="23" t="n"/>
+      <c r="I76" s="23" t="n"/>
+      <c r="J76" s="23" t="n"/>
+      <c r="K76" s="23" t="n"/>
+      <c r="L76" s="23" t="n"/>
+      <c r="M76" s="23" t="n"/>
+      <c r="N76" s="23" t="n"/>
+      <c r="O76" s="23" t="n"/>
+      <c r="P76" s="23" t="n"/>
+      <c r="Q76" s="23" t="n"/>
+      <c r="R76" s="23" t="n"/>
+      <c r="S76" s="23" t="n"/>
+      <c r="T76" s="23" t="n"/>
+      <c r="U76" s="23" t="n"/>
+      <c r="V76" s="23" t="n"/>
+      <c r="W76" s="23" t="n"/>
+      <c r="X76" s="23" t="n"/>
+      <c r="Y76" s="23" t="n"/>
+      <c r="Z76" s="23" t="n"/>
+      <c r="AA76" s="23" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  本来の納付額</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+      <c r="H77" s="9" t="n"/>
+      <c r="I77" s="9" t="n"/>
+      <c r="J77" s="9" t="n"/>
+      <c r="K77" s="9" t="n"/>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="9" t="n"/>
+      <c r="N77" s="9" t="n"/>
+      <c r="O77" s="9" t="n"/>
+      <c r="P77" s="9" t="n"/>
+      <c r="Q77" s="9" t="n"/>
+      <c r="R77" s="9" t="n"/>
+      <c r="S77" s="9" t="n"/>
+      <c r="T77" s="9" t="n"/>
+      <c r="U77" s="9" t="n"/>
+      <c r="V77" s="9" t="n"/>
+      <c r="W77" s="9" t="n"/>
+      <c r="X77" s="9" t="n"/>
+      <c r="Y77" s="9" t="n"/>
+      <c r="Z77" s="9" t="n"/>
+      <c r="AA77" s="15">
+        <f>SUM(B77:Z77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  実際の納付額</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="9" t="n"/>
+      <c r="H78" s="9" t="n"/>
+      <c r="I78" s="9" t="n"/>
+      <c r="J78" s="9" t="n"/>
+      <c r="K78" s="9" t="n"/>
+      <c r="L78" s="9" t="n"/>
+      <c r="M78" s="9" t="n"/>
+      <c r="N78" s="9" t="n"/>
+      <c r="O78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
+      <c r="Q78" s="9" t="n"/>
+      <c r="R78" s="9" t="n"/>
+      <c r="S78" s="9" t="n"/>
+      <c r="T78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
+      <c r="V78" s="9" t="n"/>
+      <c r="W78" s="9" t="n"/>
+      <c r="X78" s="9" t="n"/>
+      <c r="Y78" s="9" t="n"/>
+      <c r="Z78" s="9" t="n"/>
+      <c r="AA78" s="15">
+        <f>SUM(B78:Z78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  滞納残高（累計）</t>
+        </is>
+      </c>
+      <c r="B79" s="17">
+        <f>B77-B78</f>
+        <v/>
+      </c>
+      <c r="C79" s="17">
+        <f>B79+C77-C78</f>
+        <v/>
+      </c>
+      <c r="D79" s="17">
+        <f>C79+D77-D78</f>
+        <v/>
+      </c>
+      <c r="E79" s="17">
+        <f>D79+E77-E78</f>
+        <v/>
+      </c>
+      <c r="F79" s="17">
+        <f>E79+F77-F78</f>
+        <v/>
+      </c>
+      <c r="G79" s="17">
+        <f>F79+G77-G78</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>G79+H77-H78</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>H79+I77-I78</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>I79+J77-J78</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>J79+K77-K78</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>K79+L77-L78</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>L79+M77-M78</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>M79+N77-N78</f>
+        <v/>
+      </c>
+      <c r="O79" s="17">
+        <f>N79+O77-O78</f>
+        <v/>
+      </c>
+      <c r="P79" s="17">
+        <f>O79+P77-P78</f>
+        <v/>
+      </c>
+      <c r="Q79" s="17">
+        <f>P79+Q77-Q78</f>
+        <v/>
+      </c>
+      <c r="R79" s="17">
+        <f>Q79+R77-R78</f>
+        <v/>
+      </c>
+      <c r="S79" s="17">
+        <f>R79+S77-S78</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>S79+T77-T78</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>T79+U77-U78</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>U79+V77-V78</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>V79+W77-W78</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>W79+X77-X78</f>
+        <v/>
+      </c>
+      <c r="Y79" s="17">
+        <f>X79+Y77-Y78</f>
+        <v/>
+      </c>
+      <c r="Z79" s="17">
+        <f>Y79+Z77-Z78</f>
+        <v/>
+      </c>
+      <c r="AA79" s="17">
+        <f>Z79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>滞納残高 合計</t>
+        </is>
+      </c>
+      <c r="B80" s="19">
+        <f>B55+B59+B63+B67+B71+B75+B79</f>
+        <v/>
+      </c>
+      <c r="C80" s="19">
+        <f>C55+C59+C63+C67+C71+C75+C79</f>
+        <v/>
+      </c>
+      <c r="D80" s="19">
+        <f>D55+D59+D63+D67+D71+D75+D79</f>
+        <v/>
+      </c>
+      <c r="E80" s="19">
+        <f>E55+E59+E63+E67+E71+E75+E79</f>
+        <v/>
+      </c>
+      <c r="F80" s="19">
+        <f>F55+F59+F63+F67+F71+F75+F79</f>
+        <v/>
+      </c>
+      <c r="G80" s="19">
+        <f>G55+G59+G63+G67+G71+G75+G79</f>
+        <v/>
+      </c>
+      <c r="H80" s="19">
+        <f>H55+H59+H63+H67+H71+H75+H79</f>
+        <v/>
+      </c>
+      <c r="I80" s="19">
+        <f>I55+I59+I63+I67+I71+I75+I79</f>
+        <v/>
+      </c>
+      <c r="J80" s="19">
+        <f>J55+J59+J63+J67+J71+J75+J79</f>
+        <v/>
+      </c>
+      <c r="K80" s="19">
+        <f>K55+K59+K63+K67+K71+K75+K79</f>
+        <v/>
+      </c>
+      <c r="L80" s="19">
+        <f>L55+L59+L63+L67+L71+L75+L79</f>
+        <v/>
+      </c>
+      <c r="M80" s="19">
+        <f>M55+M59+M63+M67+M71+M75+M79</f>
+        <v/>
+      </c>
+      <c r="N80" s="19">
+        <f>N55+N59+N63+N67+N71+N75+N79</f>
+        <v/>
+      </c>
+      <c r="O80" s="19">
+        <f>O55+O59+O63+O67+O71+O75+O79</f>
+        <v/>
+      </c>
+      <c r="P80" s="19">
+        <f>P55+P59+P63+P67+P71+P75+P79</f>
+        <v/>
+      </c>
+      <c r="Q80" s="19">
+        <f>Q55+Q59+Q63+Q67+Q71+Q75+Q79</f>
+        <v/>
+      </c>
+      <c r="R80" s="19">
+        <f>R55+R59+R63+R67+R71+R75+R79</f>
+        <v/>
+      </c>
+      <c r="S80" s="19">
+        <f>S55+S59+S63+S67+S71+S75+S79</f>
+        <v/>
+      </c>
+      <c r="T80" s="19">
+        <f>T55+T59+T63+T67+T71+T75+T79</f>
+        <v/>
+      </c>
+      <c r="U80" s="19">
+        <f>U55+U59+U63+U67+U71+U75+U79</f>
+        <v/>
+      </c>
+      <c r="V80" s="19">
+        <f>V55+V59+V63+V67+V71+V75+V79</f>
+        <v/>
+      </c>
+      <c r="W80" s="19">
+        <f>W55+W59+W63+W67+W71+W75+W79</f>
+        <v/>
+      </c>
+      <c r="X80" s="19">
+        <f>X55+X59+X63+X67+X71+X75+X79</f>
+        <v/>
+      </c>
+      <c r="Y80" s="19">
+        <f>Y55+Y59+Y63+Y67+Y71+Y75+Y79</f>
+        <v/>
+      </c>
+      <c r="Z80" s="19">
+        <f>Z55+Z59+Z63+Z67+Z71+Z75+Z79</f>
+        <v/>
+      </c>
+      <c r="AA80" s="19">
+        <f>AA55+AA59+AA63+AA67+AA71+AA75+AA79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>実質残高（月末残高－滞納残高合計）</t>
+        </is>
+      </c>
+      <c r="B81" s="19">
+        <f>B48-B80</f>
+        <v/>
+      </c>
+      <c r="C81" s="19">
+        <f>C48-C80</f>
+        <v/>
+      </c>
+      <c r="D81" s="19">
+        <f>D48-D80</f>
+        <v/>
+      </c>
+      <c r="E81" s="19">
+        <f>E48-E80</f>
+        <v/>
+      </c>
+      <c r="F81" s="19">
+        <f>F48-F80</f>
+        <v/>
+      </c>
+      <c r="G81" s="19">
+        <f>G48-G80</f>
+        <v/>
+      </c>
+      <c r="H81" s="19">
+        <f>H48-H80</f>
+        <v/>
+      </c>
+      <c r="I81" s="19">
+        <f>I48-I80</f>
+        <v/>
+      </c>
+      <c r="J81" s="19">
+        <f>J48-J80</f>
+        <v/>
+      </c>
+      <c r="K81" s="19">
+        <f>K48-K80</f>
+        <v/>
+      </c>
+      <c r="L81" s="19">
+        <f>L48-L80</f>
+        <v/>
+      </c>
+      <c r="M81" s="19">
+        <f>M48-M80</f>
+        <v/>
+      </c>
+      <c r="N81" s="19">
+        <f>N48-N80</f>
+        <v/>
+      </c>
+      <c r="O81" s="19">
+        <f>O48-O80</f>
+        <v/>
+      </c>
+      <c r="P81" s="19">
+        <f>P48-P80</f>
+        <v/>
+      </c>
+      <c r="Q81" s="19">
+        <f>Q48-Q80</f>
+        <v/>
+      </c>
+      <c r="R81" s="19">
+        <f>R48-R80</f>
+        <v/>
+      </c>
+      <c r="S81" s="19">
+        <f>S48-S80</f>
+        <v/>
+      </c>
+      <c r="T81" s="19">
+        <f>T48-T80</f>
+        <v/>
+      </c>
+      <c r="U81" s="19">
+        <f>U48-U80</f>
+        <v/>
+      </c>
+      <c r="V81" s="19">
+        <f>V48-V80</f>
+        <v/>
+      </c>
+      <c r="W81" s="19">
+        <f>W48-W80</f>
+        <v/>
+      </c>
+      <c r="X81" s="19">
+        <f>X48-X80</f>
+        <v/>
+      </c>
+      <c r="Y81" s="19">
+        <f>Y48-Y80</f>
+        <v/>
+      </c>
+      <c r="Z81" s="19">
+        <f>Z48-Z80</f>
+        <v/>
+      </c>
+      <c r="AA81" s="19">
+        <f>AA48-AA80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>※滞納管理の「実際の納付額」は、上の資金収支（法定福利費・法人税・消費税等納付など）にも同じ額を入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>※営業収入の2025年10月〜2026年8月は実績値（各セルのコメントに出典）。2026年9月は集計ファイル未確認のため空欄。</t>
         </is>
@@ -3334,6 +5129,51 @@
       <formula>B$48&lt;$B$4</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B80:Z80">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>B$80&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81:Z81">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>B$81&lt;$B$4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:Z55">
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>B$55&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:Z59">
+    <cfRule type="expression" priority="5" dxfId="1">
+      <formula>B$59&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63:Z63">
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>B$63&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67:Z67">
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>B$67&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71:Z71">
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>B$71&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B75:Z75">
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>B$75&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B79:Z79">
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>B$79&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/cashflow_templates/A_月次資金繰り表_25か月.xlsx
+++ b/cashflow_templates/A_月次資金繰り表_25か月.xlsx
@@ -676,7 +676,7 @@
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. 保険料・税を払えなかった月は、下部「滞納管理」に本来の納付額と実際の納付額を入力 → 滞納残高・実質残高が自動計算</t>
+          <t xml:space="preserve">  5. 社会保険料・住民税を払えなかった月は、下部「滞納管理」に本来の納付額と実際の納付額を入力 → 滞納残高・実質残高が自動計算</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA84"/>
+  <dimension ref="A1:AA64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3345,7 +3345,7 @@
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>滞納管理（保険料・税）※資金収支の計算には含めない</t>
+          <t>滞納管理（社会保険料・住民税）※資金収支の計算には含めない</t>
         </is>
       </c>
       <c r="B51" s="22" t="n"/>
@@ -3378,7 +3378,7 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>社会保険料（健康保険・厚生年金）</t>
+          <t>社会保険料</t>
         </is>
       </c>
       <c r="B52" s="23" t="n"/>
@@ -3594,7 +3594,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>労働保険料</t>
+          <t>住民税</t>
         </is>
       </c>
       <c r="B56" s="23" t="n"/>
@@ -3808,1316 +3808,236 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>源泉所得税</t>
-        </is>
-      </c>
-      <c r="B60" s="23" t="n"/>
-      <c r="C60" s="23" t="n"/>
-      <c r="D60" s="23" t="n"/>
-      <c r="E60" s="23" t="n"/>
-      <c r="F60" s="23" t="n"/>
-      <c r="G60" s="23" t="n"/>
-      <c r="H60" s="23" t="n"/>
-      <c r="I60" s="23" t="n"/>
-      <c r="J60" s="23" t="n"/>
-      <c r="K60" s="23" t="n"/>
-      <c r="L60" s="23" t="n"/>
-      <c r="M60" s="23" t="n"/>
-      <c r="N60" s="23" t="n"/>
-      <c r="O60" s="23" t="n"/>
-      <c r="P60" s="23" t="n"/>
-      <c r="Q60" s="23" t="n"/>
-      <c r="R60" s="23" t="n"/>
-      <c r="S60" s="23" t="n"/>
-      <c r="T60" s="23" t="n"/>
-      <c r="U60" s="23" t="n"/>
-      <c r="V60" s="23" t="n"/>
-      <c r="W60" s="23" t="n"/>
-      <c r="X60" s="23" t="n"/>
-      <c r="Y60" s="23" t="n"/>
-      <c r="Z60" s="23" t="n"/>
-      <c r="AA60" s="23" t="n"/>
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>滞納残高 合計</t>
+        </is>
+      </c>
+      <c r="B60" s="19">
+        <f>B55+B59</f>
+        <v/>
+      </c>
+      <c r="C60" s="19">
+        <f>C55+C59</f>
+        <v/>
+      </c>
+      <c r="D60" s="19">
+        <f>D55+D59</f>
+        <v/>
+      </c>
+      <c r="E60" s="19">
+        <f>E55+E59</f>
+        <v/>
+      </c>
+      <c r="F60" s="19">
+        <f>F55+F59</f>
+        <v/>
+      </c>
+      <c r="G60" s="19">
+        <f>G55+G59</f>
+        <v/>
+      </c>
+      <c r="H60" s="19">
+        <f>H55+H59</f>
+        <v/>
+      </c>
+      <c r="I60" s="19">
+        <f>I55+I59</f>
+        <v/>
+      </c>
+      <c r="J60" s="19">
+        <f>J55+J59</f>
+        <v/>
+      </c>
+      <c r="K60" s="19">
+        <f>K55+K59</f>
+        <v/>
+      </c>
+      <c r="L60" s="19">
+        <f>L55+L59</f>
+        <v/>
+      </c>
+      <c r="M60" s="19">
+        <f>M55+M59</f>
+        <v/>
+      </c>
+      <c r="N60" s="19">
+        <f>N55+N59</f>
+        <v/>
+      </c>
+      <c r="O60" s="19">
+        <f>O55+O59</f>
+        <v/>
+      </c>
+      <c r="P60" s="19">
+        <f>P55+P59</f>
+        <v/>
+      </c>
+      <c r="Q60" s="19">
+        <f>Q55+Q59</f>
+        <v/>
+      </c>
+      <c r="R60" s="19">
+        <f>R55+R59</f>
+        <v/>
+      </c>
+      <c r="S60" s="19">
+        <f>S55+S59</f>
+        <v/>
+      </c>
+      <c r="T60" s="19">
+        <f>T55+T59</f>
+        <v/>
+      </c>
+      <c r="U60" s="19">
+        <f>U55+U59</f>
+        <v/>
+      </c>
+      <c r="V60" s="19">
+        <f>V55+V59</f>
+        <v/>
+      </c>
+      <c r="W60" s="19">
+        <f>W55+W59</f>
+        <v/>
+      </c>
+      <c r="X60" s="19">
+        <f>X55+X59</f>
+        <v/>
+      </c>
+      <c r="Y60" s="19">
+        <f>Y55+Y59</f>
+        <v/>
+      </c>
+      <c r="Z60" s="19">
+        <f>Z55+Z59</f>
+        <v/>
+      </c>
+      <c r="AA60" s="19">
+        <f>AA55+AA59</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  本来の納付額</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="n"/>
-      <c r="C61" s="9" t="n"/>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="9" t="n"/>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-      <c r="H61" s="9" t="n"/>
-      <c r="I61" s="9" t="n"/>
-      <c r="J61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-      <c r="L61" s="9" t="n"/>
-      <c r="M61" s="9" t="n"/>
-      <c r="N61" s="9" t="n"/>
-      <c r="O61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="9" t="n"/>
-      <c r="R61" s="9" t="n"/>
-      <c r="S61" s="9" t="n"/>
-      <c r="T61" s="9" t="n"/>
-      <c r="U61" s="9" t="n"/>
-      <c r="V61" s="9" t="n"/>
-      <c r="W61" s="9" t="n"/>
-      <c r="X61" s="9" t="n"/>
-      <c r="Y61" s="9" t="n"/>
-      <c r="Z61" s="9" t="n"/>
-      <c r="AA61" s="15">
-        <f>SUM(B61:Z61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  実際の納付額</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="9" t="n"/>
-      <c r="D62" s="9" t="n"/>
-      <c r="E62" s="9" t="n"/>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
-      <c r="H62" s="9" t="n"/>
-      <c r="I62" s="9" t="n"/>
-      <c r="J62" s="9" t="n"/>
-      <c r="K62" s="9" t="n"/>
-      <c r="L62" s="9" t="n"/>
-      <c r="M62" s="9" t="n"/>
-      <c r="N62" s="9" t="n"/>
-      <c r="O62" s="9" t="n"/>
-      <c r="P62" s="9" t="n"/>
-      <c r="Q62" s="9" t="n"/>
-      <c r="R62" s="9" t="n"/>
-      <c r="S62" s="9" t="n"/>
-      <c r="T62" s="9" t="n"/>
-      <c r="U62" s="9" t="n"/>
-      <c r="V62" s="9" t="n"/>
-      <c r="W62" s="9" t="n"/>
-      <c r="X62" s="9" t="n"/>
-      <c r="Y62" s="9" t="n"/>
-      <c r="Z62" s="9" t="n"/>
-      <c r="AA62" s="15">
-        <f>SUM(B62:Z62)</f>
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>実質残高（月末残高－滞納残高合計）</t>
+        </is>
+      </c>
+      <c r="B61" s="19">
+        <f>B48-B60</f>
+        <v/>
+      </c>
+      <c r="C61" s="19">
+        <f>C48-C60</f>
+        <v/>
+      </c>
+      <c r="D61" s="19">
+        <f>D48-D60</f>
+        <v/>
+      </c>
+      <c r="E61" s="19">
+        <f>E48-E60</f>
+        <v/>
+      </c>
+      <c r="F61" s="19">
+        <f>F48-F60</f>
+        <v/>
+      </c>
+      <c r="G61" s="19">
+        <f>G48-G60</f>
+        <v/>
+      </c>
+      <c r="H61" s="19">
+        <f>H48-H60</f>
+        <v/>
+      </c>
+      <c r="I61" s="19">
+        <f>I48-I60</f>
+        <v/>
+      </c>
+      <c r="J61" s="19">
+        <f>J48-J60</f>
+        <v/>
+      </c>
+      <c r="K61" s="19">
+        <f>K48-K60</f>
+        <v/>
+      </c>
+      <c r="L61" s="19">
+        <f>L48-L60</f>
+        <v/>
+      </c>
+      <c r="M61" s="19">
+        <f>M48-M60</f>
+        <v/>
+      </c>
+      <c r="N61" s="19">
+        <f>N48-N60</f>
+        <v/>
+      </c>
+      <c r="O61" s="19">
+        <f>O48-O60</f>
+        <v/>
+      </c>
+      <c r="P61" s="19">
+        <f>P48-P60</f>
+        <v/>
+      </c>
+      <c r="Q61" s="19">
+        <f>Q48-Q60</f>
+        <v/>
+      </c>
+      <c r="R61" s="19">
+        <f>R48-R60</f>
+        <v/>
+      </c>
+      <c r="S61" s="19">
+        <f>S48-S60</f>
+        <v/>
+      </c>
+      <c r="T61" s="19">
+        <f>T48-T60</f>
+        <v/>
+      </c>
+      <c r="U61" s="19">
+        <f>U48-U60</f>
+        <v/>
+      </c>
+      <c r="V61" s="19">
+        <f>V48-V60</f>
+        <v/>
+      </c>
+      <c r="W61" s="19">
+        <f>W48-W60</f>
+        <v/>
+      </c>
+      <c r="X61" s="19">
+        <f>X48-X60</f>
+        <v/>
+      </c>
+      <c r="Y61" s="19">
+        <f>Y48-Y60</f>
+        <v/>
+      </c>
+      <c r="Z61" s="19">
+        <f>Z48-Z60</f>
+        <v/>
+      </c>
+      <c r="AA61" s="19">
+        <f>AA48-AA60</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  滞納残高（累計）</t>
-        </is>
-      </c>
-      <c r="B63" s="17">
-        <f>B61-B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="17">
-        <f>B63+C61-C62</f>
-        <v/>
-      </c>
-      <c r="D63" s="17">
-        <f>C63+D61-D62</f>
-        <v/>
-      </c>
-      <c r="E63" s="17">
-        <f>D63+E61-E62</f>
-        <v/>
-      </c>
-      <c r="F63" s="17">
-        <f>E63+F61-F62</f>
-        <v/>
-      </c>
-      <c r="G63" s="17">
-        <f>F63+G61-G62</f>
-        <v/>
-      </c>
-      <c r="H63" s="17">
-        <f>G63+H61-H62</f>
-        <v/>
-      </c>
-      <c r="I63" s="17">
-        <f>H63+I61-I62</f>
-        <v/>
-      </c>
-      <c r="J63" s="17">
-        <f>I63+J61-J62</f>
-        <v/>
-      </c>
-      <c r="K63" s="17">
-        <f>J63+K61-K62</f>
-        <v/>
-      </c>
-      <c r="L63" s="17">
-        <f>K63+L61-L62</f>
-        <v/>
-      </c>
-      <c r="M63" s="17">
-        <f>L63+M61-M62</f>
-        <v/>
-      </c>
-      <c r="N63" s="17">
-        <f>M63+N61-N62</f>
-        <v/>
-      </c>
-      <c r="O63" s="17">
-        <f>N63+O61-O62</f>
-        <v/>
-      </c>
-      <c r="P63" s="17">
-        <f>O63+P61-P62</f>
-        <v/>
-      </c>
-      <c r="Q63" s="17">
-        <f>P63+Q61-Q62</f>
-        <v/>
-      </c>
-      <c r="R63" s="17">
-        <f>Q63+R61-R62</f>
-        <v/>
-      </c>
-      <c r="S63" s="17">
-        <f>R63+S61-S62</f>
-        <v/>
-      </c>
-      <c r="T63" s="17">
-        <f>S63+T61-T62</f>
-        <v/>
-      </c>
-      <c r="U63" s="17">
-        <f>T63+U61-U62</f>
-        <v/>
-      </c>
-      <c r="V63" s="17">
-        <f>U63+V61-V62</f>
-        <v/>
-      </c>
-      <c r="W63" s="17">
-        <f>V63+W61-W62</f>
-        <v/>
-      </c>
-      <c r="X63" s="17">
-        <f>W63+X61-X62</f>
-        <v/>
-      </c>
-      <c r="Y63" s="17">
-        <f>X63+Y61-Y62</f>
-        <v/>
-      </c>
-      <c r="Z63" s="17">
-        <f>Y63+Z61-Z62</f>
-        <v/>
-      </c>
-      <c r="AA63" s="17">
-        <f>Z63</f>
-        <v/>
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>※滞納管理の「実際の納付額」は、上の資金収支（社会保険料＝法定福利費、住民税＝人件費から天引きして納付する分など）にも同じ額を入れてください。</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>住民税（特別徴収）</t>
-        </is>
-      </c>
-      <c r="B64" s="23" t="n"/>
-      <c r="C64" s="23" t="n"/>
-      <c r="D64" s="23" t="n"/>
-      <c r="E64" s="23" t="n"/>
-      <c r="F64" s="23" t="n"/>
-      <c r="G64" s="23" t="n"/>
-      <c r="H64" s="23" t="n"/>
-      <c r="I64" s="23" t="n"/>
-      <c r="J64" s="23" t="n"/>
-      <c r="K64" s="23" t="n"/>
-      <c r="L64" s="23" t="n"/>
-      <c r="M64" s="23" t="n"/>
-      <c r="N64" s="23" t="n"/>
-      <c r="O64" s="23" t="n"/>
-      <c r="P64" s="23" t="n"/>
-      <c r="Q64" s="23" t="n"/>
-      <c r="R64" s="23" t="n"/>
-      <c r="S64" s="23" t="n"/>
-      <c r="T64" s="23" t="n"/>
-      <c r="U64" s="23" t="n"/>
-      <c r="V64" s="23" t="n"/>
-      <c r="W64" s="23" t="n"/>
-      <c r="X64" s="23" t="n"/>
-      <c r="Y64" s="23" t="n"/>
-      <c r="Z64" s="23" t="n"/>
-      <c r="AA64" s="23" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  本来の納付額</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
-      <c r="H65" s="9" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="9" t="n"/>
-      <c r="K65" s="9" t="n"/>
-      <c r="L65" s="9" t="n"/>
-      <c r="M65" s="9" t="n"/>
-      <c r="N65" s="9" t="n"/>
-      <c r="O65" s="9" t="n"/>
-      <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="9" t="n"/>
-      <c r="R65" s="9" t="n"/>
-      <c r="S65" s="9" t="n"/>
-      <c r="T65" s="9" t="n"/>
-      <c r="U65" s="9" t="n"/>
-      <c r="V65" s="9" t="n"/>
-      <c r="W65" s="9" t="n"/>
-      <c r="X65" s="9" t="n"/>
-      <c r="Y65" s="9" t="n"/>
-      <c r="Z65" s="9" t="n"/>
-      <c r="AA65" s="15">
-        <f>SUM(B65:Z65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  実際の納付額</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="n"/>
-      <c r="C66" s="9" t="n"/>
-      <c r="D66" s="9" t="n"/>
-      <c r="E66" s="9" t="n"/>
-      <c r="F66" s="9" t="n"/>
-      <c r="G66" s="9" t="n"/>
-      <c r="H66" s="9" t="n"/>
-      <c r="I66" s="9" t="n"/>
-      <c r="J66" s="9" t="n"/>
-      <c r="K66" s="9" t="n"/>
-      <c r="L66" s="9" t="n"/>
-      <c r="M66" s="9" t="n"/>
-      <c r="N66" s="9" t="n"/>
-      <c r="O66" s="9" t="n"/>
-      <c r="P66" s="9" t="n"/>
-      <c r="Q66" s="9" t="n"/>
-      <c r="R66" s="9" t="n"/>
-      <c r="S66" s="9" t="n"/>
-      <c r="T66" s="9" t="n"/>
-      <c r="U66" s="9" t="n"/>
-      <c r="V66" s="9" t="n"/>
-      <c r="W66" s="9" t="n"/>
-      <c r="X66" s="9" t="n"/>
-      <c r="Y66" s="9" t="n"/>
-      <c r="Z66" s="9" t="n"/>
-      <c r="AA66" s="15">
-        <f>SUM(B66:Z66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  滞納残高（累計）</t>
-        </is>
-      </c>
-      <c r="B67" s="17">
-        <f>B65-B66</f>
-        <v/>
-      </c>
-      <c r="C67" s="17">
-        <f>B67+C65-C66</f>
-        <v/>
-      </c>
-      <c r="D67" s="17">
-        <f>C67+D65-D66</f>
-        <v/>
-      </c>
-      <c r="E67" s="17">
-        <f>D67+E65-E66</f>
-        <v/>
-      </c>
-      <c r="F67" s="17">
-        <f>E67+F65-F66</f>
-        <v/>
-      </c>
-      <c r="G67" s="17">
-        <f>F67+G65-G66</f>
-        <v/>
-      </c>
-      <c r="H67" s="17">
-        <f>G67+H65-H66</f>
-        <v/>
-      </c>
-      <c r="I67" s="17">
-        <f>H67+I65-I66</f>
-        <v/>
-      </c>
-      <c r="J67" s="17">
-        <f>I67+J65-J66</f>
-        <v/>
-      </c>
-      <c r="K67" s="17">
-        <f>J67+K65-K66</f>
-        <v/>
-      </c>
-      <c r="L67" s="17">
-        <f>K67+L65-L66</f>
-        <v/>
-      </c>
-      <c r="M67" s="17">
-        <f>L67+M65-M66</f>
-        <v/>
-      </c>
-      <c r="N67" s="17">
-        <f>M67+N65-N66</f>
-        <v/>
-      </c>
-      <c r="O67" s="17">
-        <f>N67+O65-O66</f>
-        <v/>
-      </c>
-      <c r="P67" s="17">
-        <f>O67+P65-P66</f>
-        <v/>
-      </c>
-      <c r="Q67" s="17">
-        <f>P67+Q65-Q66</f>
-        <v/>
-      </c>
-      <c r="R67" s="17">
-        <f>Q67+R65-R66</f>
-        <v/>
-      </c>
-      <c r="S67" s="17">
-        <f>R67+S65-S66</f>
-        <v/>
-      </c>
-      <c r="T67" s="17">
-        <f>S67+T65-T66</f>
-        <v/>
-      </c>
-      <c r="U67" s="17">
-        <f>T67+U65-U66</f>
-        <v/>
-      </c>
-      <c r="V67" s="17">
-        <f>U67+V65-V66</f>
-        <v/>
-      </c>
-      <c r="W67" s="17">
-        <f>V67+W65-W66</f>
-        <v/>
-      </c>
-      <c r="X67" s="17">
-        <f>W67+X65-X66</f>
-        <v/>
-      </c>
-      <c r="Y67" s="17">
-        <f>X67+Y65-Y66</f>
-        <v/>
-      </c>
-      <c r="Z67" s="17">
-        <f>Y67+Z65-Z66</f>
-        <v/>
-      </c>
-      <c r="AA67" s="17">
-        <f>Z67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>消費税</t>
-        </is>
-      </c>
-      <c r="B68" s="23" t="n"/>
-      <c r="C68" s="23" t="n"/>
-      <c r="D68" s="23" t="n"/>
-      <c r="E68" s="23" t="n"/>
-      <c r="F68" s="23" t="n"/>
-      <c r="G68" s="23" t="n"/>
-      <c r="H68" s="23" t="n"/>
-      <c r="I68" s="23" t="n"/>
-      <c r="J68" s="23" t="n"/>
-      <c r="K68" s="23" t="n"/>
-      <c r="L68" s="23" t="n"/>
-      <c r="M68" s="23" t="n"/>
-      <c r="N68" s="23" t="n"/>
-      <c r="O68" s="23" t="n"/>
-      <c r="P68" s="23" t="n"/>
-      <c r="Q68" s="23" t="n"/>
-      <c r="R68" s="23" t="n"/>
-      <c r="S68" s="23" t="n"/>
-      <c r="T68" s="23" t="n"/>
-      <c r="U68" s="23" t="n"/>
-      <c r="V68" s="23" t="n"/>
-      <c r="W68" s="23" t="n"/>
-      <c r="X68" s="23" t="n"/>
-      <c r="Y68" s="23" t="n"/>
-      <c r="Z68" s="23" t="n"/>
-      <c r="AA68" s="23" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  本来の納付額</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="9" t="n"/>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
-      <c r="H69" s="9" t="n"/>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="9" t="n"/>
-      <c r="K69" s="9" t="n"/>
-      <c r="L69" s="9" t="n"/>
-      <c r="M69" s="9" t="n"/>
-      <c r="N69" s="9" t="n"/>
-      <c r="O69" s="9" t="n"/>
-      <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="9" t="n"/>
-      <c r="R69" s="9" t="n"/>
-      <c r="S69" s="9" t="n"/>
-      <c r="T69" s="9" t="n"/>
-      <c r="U69" s="9" t="n"/>
-      <c r="V69" s="9" t="n"/>
-      <c r="W69" s="9" t="n"/>
-      <c r="X69" s="9" t="n"/>
-      <c r="Y69" s="9" t="n"/>
-      <c r="Z69" s="9" t="n"/>
-      <c r="AA69" s="15">
-        <f>SUM(B69:Z69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  実際の納付額</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="n"/>
-      <c r="C70" s="9" t="n"/>
-      <c r="D70" s="9" t="n"/>
-      <c r="E70" s="9" t="n"/>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
-      <c r="H70" s="9" t="n"/>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="9" t="n"/>
-      <c r="K70" s="9" t="n"/>
-      <c r="L70" s="9" t="n"/>
-      <c r="M70" s="9" t="n"/>
-      <c r="N70" s="9" t="n"/>
-      <c r="O70" s="9" t="n"/>
-      <c r="P70" s="9" t="n"/>
-      <c r="Q70" s="9" t="n"/>
-      <c r="R70" s="9" t="n"/>
-      <c r="S70" s="9" t="n"/>
-      <c r="T70" s="9" t="n"/>
-      <c r="U70" s="9" t="n"/>
-      <c r="V70" s="9" t="n"/>
-      <c r="W70" s="9" t="n"/>
-      <c r="X70" s="9" t="n"/>
-      <c r="Y70" s="9" t="n"/>
-      <c r="Z70" s="9" t="n"/>
-      <c r="AA70" s="15">
-        <f>SUM(B70:Z70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  滞納残高（累計）</t>
-        </is>
-      </c>
-      <c r="B71" s="17">
-        <f>B69-B70</f>
-        <v/>
-      </c>
-      <c r="C71" s="17">
-        <f>B71+C69-C70</f>
-        <v/>
-      </c>
-      <c r="D71" s="17">
-        <f>C71+D69-D70</f>
-        <v/>
-      </c>
-      <c r="E71" s="17">
-        <f>D71+E69-E70</f>
-        <v/>
-      </c>
-      <c r="F71" s="17">
-        <f>E71+F69-F70</f>
-        <v/>
-      </c>
-      <c r="G71" s="17">
-        <f>F71+G69-G70</f>
-        <v/>
-      </c>
-      <c r="H71" s="17">
-        <f>G71+H69-H70</f>
-        <v/>
-      </c>
-      <c r="I71" s="17">
-        <f>H71+I69-I70</f>
-        <v/>
-      </c>
-      <c r="J71" s="17">
-        <f>I71+J69-J70</f>
-        <v/>
-      </c>
-      <c r="K71" s="17">
-        <f>J71+K69-K70</f>
-        <v/>
-      </c>
-      <c r="L71" s="17">
-        <f>K71+L69-L70</f>
-        <v/>
-      </c>
-      <c r="M71" s="17">
-        <f>L71+M69-M70</f>
-        <v/>
-      </c>
-      <c r="N71" s="17">
-        <f>M71+N69-N70</f>
-        <v/>
-      </c>
-      <c r="O71" s="17">
-        <f>N71+O69-O70</f>
-        <v/>
-      </c>
-      <c r="P71" s="17">
-        <f>O71+P69-P70</f>
-        <v/>
-      </c>
-      <c r="Q71" s="17">
-        <f>P71+Q69-Q70</f>
-        <v/>
-      </c>
-      <c r="R71" s="17">
-        <f>Q71+R69-R70</f>
-        <v/>
-      </c>
-      <c r="S71" s="17">
-        <f>R71+S69-S70</f>
-        <v/>
-      </c>
-      <c r="T71" s="17">
-        <f>S71+T69-T70</f>
-        <v/>
-      </c>
-      <c r="U71" s="17">
-        <f>T71+U69-U70</f>
-        <v/>
-      </c>
-      <c r="V71" s="17">
-        <f>U71+V69-V70</f>
-        <v/>
-      </c>
-      <c r="W71" s="17">
-        <f>V71+W69-W70</f>
-        <v/>
-      </c>
-      <c r="X71" s="17">
-        <f>W71+X69-X70</f>
-        <v/>
-      </c>
-      <c r="Y71" s="17">
-        <f>X71+Y69-Y70</f>
-        <v/>
-      </c>
-      <c r="Z71" s="17">
-        <f>Y71+Z69-Z70</f>
-        <v/>
-      </c>
-      <c r="AA71" s="17">
-        <f>Z71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>法人税・地方税等</t>
-        </is>
-      </c>
-      <c r="B72" s="23" t="n"/>
-      <c r="C72" s="23" t="n"/>
-      <c r="D72" s="23" t="n"/>
-      <c r="E72" s="23" t="n"/>
-      <c r="F72" s="23" t="n"/>
-      <c r="G72" s="23" t="n"/>
-      <c r="H72" s="23" t="n"/>
-      <c r="I72" s="23" t="n"/>
-      <c r="J72" s="23" t="n"/>
-      <c r="K72" s="23" t="n"/>
-      <c r="L72" s="23" t="n"/>
-      <c r="M72" s="23" t="n"/>
-      <c r="N72" s="23" t="n"/>
-      <c r="O72" s="23" t="n"/>
-      <c r="P72" s="23" t="n"/>
-      <c r="Q72" s="23" t="n"/>
-      <c r="R72" s="23" t="n"/>
-      <c r="S72" s="23" t="n"/>
-      <c r="T72" s="23" t="n"/>
-      <c r="U72" s="23" t="n"/>
-      <c r="V72" s="23" t="n"/>
-      <c r="W72" s="23" t="n"/>
-      <c r="X72" s="23" t="n"/>
-      <c r="Y72" s="23" t="n"/>
-      <c r="Z72" s="23" t="n"/>
-      <c r="AA72" s="23" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  本来の納付額</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="9" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
-      <c r="H73" s="9" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="9" t="n"/>
-      <c r="K73" s="9" t="n"/>
-      <c r="L73" s="9" t="n"/>
-      <c r="M73" s="9" t="n"/>
-      <c r="N73" s="9" t="n"/>
-      <c r="O73" s="9" t="n"/>
-      <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="9" t="n"/>
-      <c r="R73" s="9" t="n"/>
-      <c r="S73" s="9" t="n"/>
-      <c r="T73" s="9" t="n"/>
-      <c r="U73" s="9" t="n"/>
-      <c r="V73" s="9" t="n"/>
-      <c r="W73" s="9" t="n"/>
-      <c r="X73" s="9" t="n"/>
-      <c r="Y73" s="9" t="n"/>
-      <c r="Z73" s="9" t="n"/>
-      <c r="AA73" s="15">
-        <f>SUM(B73:Z73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  実際の納付額</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
-      <c r="H74" s="9" t="n"/>
-      <c r="I74" s="9" t="n"/>
-      <c r="J74" s="9" t="n"/>
-      <c r="K74" s="9" t="n"/>
-      <c r="L74" s="9" t="n"/>
-      <c r="M74" s="9" t="n"/>
-      <c r="N74" s="9" t="n"/>
-      <c r="O74" s="9" t="n"/>
-      <c r="P74" s="9" t="n"/>
-      <c r="Q74" s="9" t="n"/>
-      <c r="R74" s="9" t="n"/>
-      <c r="S74" s="9" t="n"/>
-      <c r="T74" s="9" t="n"/>
-      <c r="U74" s="9" t="n"/>
-      <c r="V74" s="9" t="n"/>
-      <c r="W74" s="9" t="n"/>
-      <c r="X74" s="9" t="n"/>
-      <c r="Y74" s="9" t="n"/>
-      <c r="Z74" s="9" t="n"/>
-      <c r="AA74" s="15">
-        <f>SUM(B74:Z74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  滞納残高（累計）</t>
-        </is>
-      </c>
-      <c r="B75" s="17">
-        <f>B73-B74</f>
-        <v/>
-      </c>
-      <c r="C75" s="17">
-        <f>B75+C73-C74</f>
-        <v/>
-      </c>
-      <c r="D75" s="17">
-        <f>C75+D73-D74</f>
-        <v/>
-      </c>
-      <c r="E75" s="17">
-        <f>D75+E73-E74</f>
-        <v/>
-      </c>
-      <c r="F75" s="17">
-        <f>E75+F73-F74</f>
-        <v/>
-      </c>
-      <c r="G75" s="17">
-        <f>F75+G73-G74</f>
-        <v/>
-      </c>
-      <c r="H75" s="17">
-        <f>G75+H73-H74</f>
-        <v/>
-      </c>
-      <c r="I75" s="17">
-        <f>H75+I73-I74</f>
-        <v/>
-      </c>
-      <c r="J75" s="17">
-        <f>I75+J73-J74</f>
-        <v/>
-      </c>
-      <c r="K75" s="17">
-        <f>J75+K73-K74</f>
-        <v/>
-      </c>
-      <c r="L75" s="17">
-        <f>K75+L73-L74</f>
-        <v/>
-      </c>
-      <c r="M75" s="17">
-        <f>L75+M73-M74</f>
-        <v/>
-      </c>
-      <c r="N75" s="17">
-        <f>M75+N73-N74</f>
-        <v/>
-      </c>
-      <c r="O75" s="17">
-        <f>N75+O73-O74</f>
-        <v/>
-      </c>
-      <c r="P75" s="17">
-        <f>O75+P73-P74</f>
-        <v/>
-      </c>
-      <c r="Q75" s="17">
-        <f>P75+Q73-Q74</f>
-        <v/>
-      </c>
-      <c r="R75" s="17">
-        <f>Q75+R73-R74</f>
-        <v/>
-      </c>
-      <c r="S75" s="17">
-        <f>R75+S73-S74</f>
-        <v/>
-      </c>
-      <c r="T75" s="17">
-        <f>S75+T73-T74</f>
-        <v/>
-      </c>
-      <c r="U75" s="17">
-        <f>T75+U73-U74</f>
-        <v/>
-      </c>
-      <c r="V75" s="17">
-        <f>U75+V73-V74</f>
-        <v/>
-      </c>
-      <c r="W75" s="17">
-        <f>V75+W73-W74</f>
-        <v/>
-      </c>
-      <c r="X75" s="17">
-        <f>W75+X73-X74</f>
-        <v/>
-      </c>
-      <c r="Y75" s="17">
-        <f>X75+Y73-Y74</f>
-        <v/>
-      </c>
-      <c r="Z75" s="17">
-        <f>Y75+Z73-Z74</f>
-        <v/>
-      </c>
-      <c r="AA75" s="17">
-        <f>Z75</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>その他（延滞金等）</t>
-        </is>
-      </c>
-      <c r="B76" s="23" t="n"/>
-      <c r="C76" s="23" t="n"/>
-      <c r="D76" s="23" t="n"/>
-      <c r="E76" s="23" t="n"/>
-      <c r="F76" s="23" t="n"/>
-      <c r="G76" s="23" t="n"/>
-      <c r="H76" s="23" t="n"/>
-      <c r="I76" s="23" t="n"/>
-      <c r="J76" s="23" t="n"/>
-      <c r="K76" s="23" t="n"/>
-      <c r="L76" s="23" t="n"/>
-      <c r="M76" s="23" t="n"/>
-      <c r="N76" s="23" t="n"/>
-      <c r="O76" s="23" t="n"/>
-      <c r="P76" s="23" t="n"/>
-      <c r="Q76" s="23" t="n"/>
-      <c r="R76" s="23" t="n"/>
-      <c r="S76" s="23" t="n"/>
-      <c r="T76" s="23" t="n"/>
-      <c r="U76" s="23" t="n"/>
-      <c r="V76" s="23" t="n"/>
-      <c r="W76" s="23" t="n"/>
-      <c r="X76" s="23" t="n"/>
-      <c r="Y76" s="23" t="n"/>
-      <c r="Z76" s="23" t="n"/>
-      <c r="AA76" s="23" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  本来の納付額</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="n"/>
-      <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="9" t="n"/>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="9" t="n"/>
-      <c r="H77" s="9" t="n"/>
-      <c r="I77" s="9" t="n"/>
-      <c r="J77" s="9" t="n"/>
-      <c r="K77" s="9" t="n"/>
-      <c r="L77" s="9" t="n"/>
-      <c r="M77" s="9" t="n"/>
-      <c r="N77" s="9" t="n"/>
-      <c r="O77" s="9" t="n"/>
-      <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="9" t="n"/>
-      <c r="R77" s="9" t="n"/>
-      <c r="S77" s="9" t="n"/>
-      <c r="T77" s="9" t="n"/>
-      <c r="U77" s="9" t="n"/>
-      <c r="V77" s="9" t="n"/>
-      <c r="W77" s="9" t="n"/>
-      <c r="X77" s="9" t="n"/>
-      <c r="Y77" s="9" t="n"/>
-      <c r="Z77" s="9" t="n"/>
-      <c r="AA77" s="15">
-        <f>SUM(B77:Z77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  実際の納付額</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="9" t="n"/>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="9" t="n"/>
-      <c r="F78" s="9" t="n"/>
-      <c r="G78" s="9" t="n"/>
-      <c r="H78" s="9" t="n"/>
-      <c r="I78" s="9" t="n"/>
-      <c r="J78" s="9" t="n"/>
-      <c r="K78" s="9" t="n"/>
-      <c r="L78" s="9" t="n"/>
-      <c r="M78" s="9" t="n"/>
-      <c r="N78" s="9" t="n"/>
-      <c r="O78" s="9" t="n"/>
-      <c r="P78" s="9" t="n"/>
-      <c r="Q78" s="9" t="n"/>
-      <c r="R78" s="9" t="n"/>
-      <c r="S78" s="9" t="n"/>
-      <c r="T78" s="9" t="n"/>
-      <c r="U78" s="9" t="n"/>
-      <c r="V78" s="9" t="n"/>
-      <c r="W78" s="9" t="n"/>
-      <c r="X78" s="9" t="n"/>
-      <c r="Y78" s="9" t="n"/>
-      <c r="Z78" s="9" t="n"/>
-      <c r="AA78" s="15">
-        <f>SUM(B78:Z78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  滞納残高（累計）</t>
-        </is>
-      </c>
-      <c r="B79" s="17">
-        <f>B77-B78</f>
-        <v/>
-      </c>
-      <c r="C79" s="17">
-        <f>B79+C77-C78</f>
-        <v/>
-      </c>
-      <c r="D79" s="17">
-        <f>C79+D77-D78</f>
-        <v/>
-      </c>
-      <c r="E79" s="17">
-        <f>D79+E77-E78</f>
-        <v/>
-      </c>
-      <c r="F79" s="17">
-        <f>E79+F77-F78</f>
-        <v/>
-      </c>
-      <c r="G79" s="17">
-        <f>F79+G77-G78</f>
-        <v/>
-      </c>
-      <c r="H79" s="17">
-        <f>G79+H77-H78</f>
-        <v/>
-      </c>
-      <c r="I79" s="17">
-        <f>H79+I77-I78</f>
-        <v/>
-      </c>
-      <c r="J79" s="17">
-        <f>I79+J77-J78</f>
-        <v/>
-      </c>
-      <c r="K79" s="17">
-        <f>J79+K77-K78</f>
-        <v/>
-      </c>
-      <c r="L79" s="17">
-        <f>K79+L77-L78</f>
-        <v/>
-      </c>
-      <c r="M79" s="17">
-        <f>L79+M77-M78</f>
-        <v/>
-      </c>
-      <c r="N79" s="17">
-        <f>M79+N77-N78</f>
-        <v/>
-      </c>
-      <c r="O79" s="17">
-        <f>N79+O77-O78</f>
-        <v/>
-      </c>
-      <c r="P79" s="17">
-        <f>O79+P77-P78</f>
-        <v/>
-      </c>
-      <c r="Q79" s="17">
-        <f>P79+Q77-Q78</f>
-        <v/>
-      </c>
-      <c r="R79" s="17">
-        <f>Q79+R77-R78</f>
-        <v/>
-      </c>
-      <c r="S79" s="17">
-        <f>R79+S77-S78</f>
-        <v/>
-      </c>
-      <c r="T79" s="17">
-        <f>S79+T77-T78</f>
-        <v/>
-      </c>
-      <c r="U79" s="17">
-        <f>T79+U77-U78</f>
-        <v/>
-      </c>
-      <c r="V79" s="17">
-        <f>U79+V77-V78</f>
-        <v/>
-      </c>
-      <c r="W79" s="17">
-        <f>V79+W77-W78</f>
-        <v/>
-      </c>
-      <c r="X79" s="17">
-        <f>W79+X77-X78</f>
-        <v/>
-      </c>
-      <c r="Y79" s="17">
-        <f>X79+Y77-Y78</f>
-        <v/>
-      </c>
-      <c r="Z79" s="17">
-        <f>Y79+Z77-Z78</f>
-        <v/>
-      </c>
-      <c r="AA79" s="17">
-        <f>Z79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="18" t="inlineStr">
-        <is>
-          <t>滞納残高 合計</t>
-        </is>
-      </c>
-      <c r="B80" s="19">
-        <f>B55+B59+B63+B67+B71+B75+B79</f>
-        <v/>
-      </c>
-      <c r="C80" s="19">
-        <f>C55+C59+C63+C67+C71+C75+C79</f>
-        <v/>
-      </c>
-      <c r="D80" s="19">
-        <f>D55+D59+D63+D67+D71+D75+D79</f>
-        <v/>
-      </c>
-      <c r="E80" s="19">
-        <f>E55+E59+E63+E67+E71+E75+E79</f>
-        <v/>
-      </c>
-      <c r="F80" s="19">
-        <f>F55+F59+F63+F67+F71+F75+F79</f>
-        <v/>
-      </c>
-      <c r="G80" s="19">
-        <f>G55+G59+G63+G67+G71+G75+G79</f>
-        <v/>
-      </c>
-      <c r="H80" s="19">
-        <f>H55+H59+H63+H67+H71+H75+H79</f>
-        <v/>
-      </c>
-      <c r="I80" s="19">
-        <f>I55+I59+I63+I67+I71+I75+I79</f>
-        <v/>
-      </c>
-      <c r="J80" s="19">
-        <f>J55+J59+J63+J67+J71+J75+J79</f>
-        <v/>
-      </c>
-      <c r="K80" s="19">
-        <f>K55+K59+K63+K67+K71+K75+K79</f>
-        <v/>
-      </c>
-      <c r="L80" s="19">
-        <f>L55+L59+L63+L67+L71+L75+L79</f>
-        <v/>
-      </c>
-      <c r="M80" s="19">
-        <f>M55+M59+M63+M67+M71+M75+M79</f>
-        <v/>
-      </c>
-      <c r="N80" s="19">
-        <f>N55+N59+N63+N67+N71+N75+N79</f>
-        <v/>
-      </c>
-      <c r="O80" s="19">
-        <f>O55+O59+O63+O67+O71+O75+O79</f>
-        <v/>
-      </c>
-      <c r="P80" s="19">
-        <f>P55+P59+P63+P67+P71+P75+P79</f>
-        <v/>
-      </c>
-      <c r="Q80" s="19">
-        <f>Q55+Q59+Q63+Q67+Q71+Q75+Q79</f>
-        <v/>
-      </c>
-      <c r="R80" s="19">
-        <f>R55+R59+R63+R67+R71+R75+R79</f>
-        <v/>
-      </c>
-      <c r="S80" s="19">
-        <f>S55+S59+S63+S67+S71+S75+S79</f>
-        <v/>
-      </c>
-      <c r="T80" s="19">
-        <f>T55+T59+T63+T67+T71+T75+T79</f>
-        <v/>
-      </c>
-      <c r="U80" s="19">
-        <f>U55+U59+U63+U67+U71+U75+U79</f>
-        <v/>
-      </c>
-      <c r="V80" s="19">
-        <f>V55+V59+V63+V67+V71+V75+V79</f>
-        <v/>
-      </c>
-      <c r="W80" s="19">
-        <f>W55+W59+W63+W67+W71+W75+W79</f>
-        <v/>
-      </c>
-      <c r="X80" s="19">
-        <f>X55+X59+X63+X67+X71+X75+X79</f>
-        <v/>
-      </c>
-      <c r="Y80" s="19">
-        <f>Y55+Y59+Y63+Y67+Y71+Y75+Y79</f>
-        <v/>
-      </c>
-      <c r="Z80" s="19">
-        <f>Z55+Z59+Z63+Z67+Z71+Z75+Z79</f>
-        <v/>
-      </c>
-      <c r="AA80" s="19">
-        <f>AA55+AA59+AA63+AA67+AA71+AA75+AA79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="18" t="inlineStr">
-        <is>
-          <t>実質残高（月末残高－滞納残高合計）</t>
-        </is>
-      </c>
-      <c r="B81" s="19">
-        <f>B48-B80</f>
-        <v/>
-      </c>
-      <c r="C81" s="19">
-        <f>C48-C80</f>
-        <v/>
-      </c>
-      <c r="D81" s="19">
-        <f>D48-D80</f>
-        <v/>
-      </c>
-      <c r="E81" s="19">
-        <f>E48-E80</f>
-        <v/>
-      </c>
-      <c r="F81" s="19">
-        <f>F48-F80</f>
-        <v/>
-      </c>
-      <c r="G81" s="19">
-        <f>G48-G80</f>
-        <v/>
-      </c>
-      <c r="H81" s="19">
-        <f>H48-H80</f>
-        <v/>
-      </c>
-      <c r="I81" s="19">
-        <f>I48-I80</f>
-        <v/>
-      </c>
-      <c r="J81" s="19">
-        <f>J48-J80</f>
-        <v/>
-      </c>
-      <c r="K81" s="19">
-        <f>K48-K80</f>
-        <v/>
-      </c>
-      <c r="L81" s="19">
-        <f>L48-L80</f>
-        <v/>
-      </c>
-      <c r="M81" s="19">
-        <f>M48-M80</f>
-        <v/>
-      </c>
-      <c r="N81" s="19">
-        <f>N48-N80</f>
-        <v/>
-      </c>
-      <c r="O81" s="19">
-        <f>O48-O80</f>
-        <v/>
-      </c>
-      <c r="P81" s="19">
-        <f>P48-P80</f>
-        <v/>
-      </c>
-      <c r="Q81" s="19">
-        <f>Q48-Q80</f>
-        <v/>
-      </c>
-      <c r="R81" s="19">
-        <f>R48-R80</f>
-        <v/>
-      </c>
-      <c r="S81" s="19">
-        <f>S48-S80</f>
-        <v/>
-      </c>
-      <c r="T81" s="19">
-        <f>T48-T80</f>
-        <v/>
-      </c>
-      <c r="U81" s="19">
-        <f>U48-U80</f>
-        <v/>
-      </c>
-      <c r="V81" s="19">
-        <f>V48-V80</f>
-        <v/>
-      </c>
-      <c r="W81" s="19">
-        <f>W48-W80</f>
-        <v/>
-      </c>
-      <c r="X81" s="19">
-        <f>X48-X80</f>
-        <v/>
-      </c>
-      <c r="Y81" s="19">
-        <f>Y48-Y80</f>
-        <v/>
-      </c>
-      <c r="Z81" s="19">
-        <f>Z48-Z80</f>
-        <v/>
-      </c>
-      <c r="AA81" s="19">
-        <f>AA48-AA80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>※滞納管理の「実際の納付額」は、上の資金収支（法定福利費・法人税・消費税等納付など）にも同じ額を入れてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>※営業収入の2025年10月〜2026年8月は実績値（各セルのコメントに出典）。2026年9月は集計ファイル未確認のため空欄。</t>
         </is>
@@ -5129,14 +4049,14 @@
       <formula>B$48&lt;$B$4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B80:Z80">
+  <conditionalFormatting sqref="B60:Z60">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>B$80&gt;0</formula>
+      <formula>B$60&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B81:Z81">
+  <conditionalFormatting sqref="B61:Z61">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>B$81&lt;$B$4</formula>
+      <formula>B$61&lt;$B$4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55:Z55">
@@ -5149,31 +4069,6 @@
       <formula>B$59&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:Z63">
-    <cfRule type="expression" priority="6" dxfId="1">
-      <formula>B$63&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67:Z67">
-    <cfRule type="expression" priority="7" dxfId="1">
-      <formula>B$67&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71:Z71">
-    <cfRule type="expression" priority="8" dxfId="1">
-      <formula>B$71&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B75:Z75">
-    <cfRule type="expression" priority="9" dxfId="1">
-      <formula>B$75&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B79:Z79">
-    <cfRule type="expression" priority="10" dxfId="1">
-      <formula>B$79&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
